--- a/درب-سجل-المؤشرات-الموحّد-2026.xlsx
+++ b/درب-سجل-المؤشرات-الموحّد-2026.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="سجل المؤشرات" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'سجل المؤشرات'!$A$3:$AC$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'سجل المؤشرات'!$A$3:$AC$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -995,11 +995,11 @@
         </is>
       </c>
       <c r="D17" s="15">
-        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$161,"التوسع في المواقع")</f>
+        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$146,"التوسع في المواقع")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$M$4:$M$161,"التوسع في المواقع"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$M$4:$M$146,"التوسع في المواقع"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1015,11 +1015,11 @@
         </is>
       </c>
       <c r="D18" s="15">
-        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$161,"الامتياز التجاري")</f>
+        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$146,"الامتياز التجاري")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$M$4:$M$161,"الامتياز التجاري"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$M$4:$M$146,"الامتياز التجاري"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1035,11 +1035,11 @@
         </is>
       </c>
       <c r="D19" s="15">
-        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$161,"زيادة وصول العملاء")</f>
+        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$146,"زيادة وصول العملاء")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$M$4:$M$161,"زيادة وصول العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$M$4:$M$146,"زيادة وصول العملاء"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1055,11 +1055,11 @@
         </is>
       </c>
       <c r="D20" s="15">
-        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$161,"إطلاق مشاريع جديدة")</f>
+        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$146,"إطلاق مشاريع جديدة")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$M$4:$M$161,"إطلاق مشاريع جديدة"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$M$4:$M$146,"إطلاق مشاريع جديدة"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1075,11 +1075,11 @@
         </is>
       </c>
       <c r="D21" s="15">
-        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$161,"تطوير التصاميم والهوية")</f>
+        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$146,"تطوير التصاميم والهوية")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$M$4:$M$161,"تطوير التصاميم والهوية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$M$4:$M$146,"تطوير التصاميم والهوية"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1095,11 +1095,11 @@
         </is>
       </c>
       <c r="D22" s="15">
-        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$161,"التحول التقني")</f>
+        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$146,"التحول التقني")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$M$4:$M$161,"التحول التقني"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$M$4:$M$146,"التحول التقني"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1115,11 +1115,11 @@
         </is>
       </c>
       <c r="D23" s="15">
-        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$161,"ساحات درب")</f>
+        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$146,"ساحات درب")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$M$4:$M$161,"ساحات درب"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$M$4:$M$146,"ساحات درب"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1135,11 +1135,11 @@
         </is>
       </c>
       <c r="D24" s="15">
-        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$161,"تطبيق «تانكي»")</f>
+        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$146,"تطبيق «تانكي»")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$M$4:$M$161,"تطبيق «تانكي»"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$M$4:$M$146,"تطبيق «تانكي»"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1155,11 +1155,11 @@
         </is>
       </c>
       <c r="D25" s="15">
-        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$161,"تعزيز تجربة العملاء")</f>
+        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$146,"تعزيز تجربة العملاء")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$M$4:$M$161,"تعزيز تجربة العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$M$4:$M$146,"تعزيز تجربة العملاء"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1175,11 +1175,11 @@
         </is>
       </c>
       <c r="D26" s="15">
-        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$161,"جودة التشغيل")</f>
+        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$146,"جودة التشغيل")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$M$4:$M$161,"جودة التشغيل"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$M$4:$M$146,"جودة التشغيل"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1195,11 +1195,11 @@
         </is>
       </c>
       <c r="D27" s="15">
-        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$161,"منظومة التأجير")</f>
+        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$146,"منظومة التأجير")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$M$4:$M$161,"منظومة التأجير"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$M$4:$M$146,"منظومة التأجير"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="D28" s="15">
-        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$161,"الاستثمار في الموظفين")</f>
+        <f>COUNTIF('سجل المؤشرات'!$M$4:$M$146,"الاستثمار في الموظفين")</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$M$4:$M$161,"الاستثمار في الموظفين"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$M$4:$M$146,"الاستثمار في الموظفين"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1282,19 +1282,19 @@
     </row>
     <row r="5">
       <c r="B5" s="19">
-        <f>IFERROR(AVERAGE('سجل المؤشرات'!$AB$4:$AB$161),0)</f>
+        <f>IFERROR(AVERAGE('سجل المؤشرات'!$AB$4:$AB$146),0)</f>
         <v/>
       </c>
       <c r="C5" s="20">
-        <f>COUNTIF('سجل المؤشرات'!$AC$4:$AC$161,"✅ محقق")</f>
+        <f>COUNTIF('سجل المؤشرات'!$AC$4:$AC$146,"✅ محقق")</f>
         <v/>
       </c>
       <c r="D5" s="20">
-        <f>COUNTIF('سجل المؤشرات'!$AC$4:$AC$161,"🟡 قريب")</f>
+        <f>COUNTIF('سجل المؤشرات'!$AC$4:$AC$146,"🟡 قريب")</f>
         <v/>
       </c>
       <c r="E5" s="20">
-        <f>COUNTIF('سجل المؤشرات'!$AC$4:$AC$161,"🔴 تحت الهدف")</f>
+        <f>COUNTIF('سجل المؤشرات'!$AC$4:$AC$146,"🔴 تحت الهدف")</f>
         <v/>
       </c>
     </row>
@@ -1347,11 +1347,11 @@
         </is>
       </c>
       <c r="C9" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$B$4:$B$161,"الإدارة التنفيذية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$B$4:$B$146,"الإدارة التنفيذية"),"—")</f>
         <v/>
       </c>
       <c r="D9" s="14">
-        <f>COUNTIF('سجل المؤشرات'!$B$4:$B$161,"الإدارة التنفيذية")</f>
+        <f>COUNTIF('سجل المؤشرات'!$B$4:$B$146,"الإدارة التنفيذية")</f>
         <v/>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="G9" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$L$4:$L$161,"النمو"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$L$4:$L$146,"النمو"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1371,11 +1371,11 @@
         </is>
       </c>
       <c r="C10" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$B$4:$B$161,"الامتياز التجاري"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$B$4:$B$146,"الامتياز التجاري"),"—")</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>COUNTIF('سجل المؤشرات'!$B$4:$B$161,"الامتياز التجاري")</f>
+        <f>COUNTIF('سجل المؤشرات'!$B$4:$B$146,"الامتياز التجاري")</f>
         <v/>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="G10" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$L$4:$L$161,"الابتكار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$L$4:$L$146,"الابتكار"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="C11" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$B$4:$B$161,"التشغيل والمحطات"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$B$4:$B$146,"التشغيل والمحطات"),"—")</f>
         <v/>
       </c>
       <c r="D11" s="14">
-        <f>COUNTIF('سجل المؤشرات'!$B$4:$B$161,"التشغيل والمحطات")</f>
+        <f>COUNTIF('سجل المؤشرات'!$B$4:$B$146,"التشغيل والمحطات")</f>
         <v/>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="G11" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$L$4:$L$161,"الاستدامة"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$L$4:$L$146,"الاستدامة"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1419,11 +1419,11 @@
         </is>
       </c>
       <c r="C12" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$B$4:$B$161,"الاستثمار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$B$4:$B$146,"الاستثمار"),"—")</f>
         <v/>
       </c>
       <c r="D12" s="14">
-        <f>COUNTIF('سجل المؤشرات'!$B$4:$B$161,"الاستثمار")</f>
+        <f>COUNTIF('سجل المؤشرات'!$B$4:$B$146,"الاستثمار")</f>
         <v/>
       </c>
     </row>
@@ -1434,11 +1434,11 @@
         </is>
       </c>
       <c r="C13" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$B$4:$B$161,"العقار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$B$4:$B$146,"العقار"),"—")</f>
         <v/>
       </c>
       <c r="D13" s="14">
-        <f>COUNTIF('سجل المؤشرات'!$B$4:$B$161,"العقار")</f>
+        <f>COUNTIF('سجل المؤشرات'!$B$4:$B$146,"العقار")</f>
         <v/>
       </c>
       <c r="F13" s="17" t="inlineStr">
@@ -1455,11 +1455,11 @@
         </is>
       </c>
       <c r="C14" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$B$4:$B$161,"التقنية الرقمية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$B$4:$B$146,"التقنية الرقمية"),"—")</f>
         <v/>
       </c>
       <c r="D14" s="14">
-        <f>COUNTIF('سجل المؤشرات'!$B$4:$B$161,"التقنية الرقمية")</f>
+        <f>COUNTIF('سجل المؤشرات'!$B$4:$B$146,"التقنية الرقمية")</f>
         <v/>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$N$4:$N$161,"مالي"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$N$4:$N$146,"مالي"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1479,11 +1479,11 @@
         </is>
       </c>
       <c r="C15" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$B$4:$B$161,"الموارد البشرية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$B$4:$B$146,"الموارد البشرية"),"—")</f>
         <v/>
       </c>
       <c r="D15" s="14">
-        <f>COUNTIF('سجل المؤشرات'!$B$4:$B$161,"الموارد البشرية")</f>
+        <f>COUNTIF('سجل المؤشرات'!$B$4:$B$146,"الموارد البشرية")</f>
         <v/>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="G15" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$N$4:$N$161,"العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$N$4:$N$146,"العملاء"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1503,11 +1503,11 @@
         </is>
       </c>
       <c r="C16" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$B$4:$B$161,"التسويق"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$B$4:$B$146,"التسويق"),"—")</f>
         <v/>
       </c>
       <c r="D16" s="14">
-        <f>COUNTIF('سجل المؤشرات'!$B$4:$B$161,"التسويق")</f>
+        <f>COUNTIF('سجل المؤشرات'!$B$4:$B$146,"التسويق")</f>
         <v/>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$N$4:$N$161,"العمليات الداخلية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$N$4:$N$146,"العمليات الداخلية"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="G17" s="16">
-        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$161,'سجل المؤشرات'!$N$4:$N$161,"التعلّم والنمو"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('سجل المؤشرات'!$AB$4:$AB$146,'سجل المؤشرات'!$N$4:$N$146,"التعلّم والنمو"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC161"/>
+  <dimension ref="A1:AC146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -10908,17 +10908,17 @@
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>أداء المشاريع</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>نظام أتمتة الكاش (Cash-In) في المحطات</t>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
         </is>
       </c>
       <c r="E106" s="25" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F106" s="25" t="inlineStr">
@@ -10933,18 +10933,18 @@
       </c>
       <c r="H106" s="26" t="inlineStr">
         <is>
-          <t>🔴 رئيسي</t>
+          <t>🟠 مهم</t>
         </is>
       </c>
       <c r="I106" s="27" t="n">
-        <v>0.04762</v>
-      </c>
-      <c r="J106" s="28" t="n">
-        <v>164</v>
+        <v>0.1</v>
+      </c>
+      <c r="J106" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="K106" s="29" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="L106" s="30" t="inlineStr">
@@ -10962,21 +10962,21 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="O106" s="32" t="n"/>
-      <c r="P106" s="32" t="n"/>
-      <c r="Q106" s="32" t="n"/>
-      <c r="R106" s="32" t="n"/>
-      <c r="S106" s="32" t="n"/>
-      <c r="T106" s="32" t="n">
-        <v>59</v>
-      </c>
-      <c r="U106" s="32" t="n"/>
-      <c r="V106" s="32" t="n"/>
-      <c r="W106" s="32" t="n"/>
-      <c r="X106" s="32" t="n"/>
-      <c r="Y106" s="32" t="n"/>
-      <c r="Z106" s="32" t="n"/>
-      <c r="AA106" s="33">
+      <c r="O106" s="36" t="n"/>
+      <c r="P106" s="36" t="n"/>
+      <c r="Q106" s="36" t="n"/>
+      <c r="R106" s="36" t="n"/>
+      <c r="S106" s="36" t="n"/>
+      <c r="T106" s="36" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U106" s="36" t="n"/>
+      <c r="V106" s="36" t="n"/>
+      <c r="W106" s="36" t="n"/>
+      <c r="X106" s="36" t="n"/>
+      <c r="Y106" s="36" t="n"/>
+      <c r="Z106" s="36" t="n"/>
+      <c r="AA106" s="37">
         <f>IF($G106="SUM",IF(COUNT($O106:$Z106)=0,"",SUM($O106:$Z106)),IF($G106="AVG",IFERROR(AVERAGE($O106:$Z106),""),IF($G106="LAST",IFERROR(LOOKUP(2,1/($O106:$Z106&lt;&gt;""),$O106:$Z106),""),"")))</f>
         <v/>
       </c>
@@ -11000,17 +11000,17 @@
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>أداء المشاريع</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>D365 FNO — المرحلة الأولى</t>
+          <t>معدل تسليم المشاريع في الموعد المحدد</t>
         </is>
       </c>
       <c r="E107" s="25" t="inlineStr">
         <is>
-          <t>وحدة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F107" s="25" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="G107" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="H107" s="26" t="inlineStr">
@@ -11029,14 +11029,14 @@
         </is>
       </c>
       <c r="I107" s="27" t="n">
-        <v>0.03175</v>
-      </c>
-      <c r="J107" s="38" t="n">
-        <v>5</v>
+        <v>0.1</v>
+      </c>
+      <c r="J107" s="27" t="n">
+        <v>0.9</v>
       </c>
       <c r="K107" s="29" t="inlineStr">
         <is>
-          <t>5 وحدات</t>
+          <t>≥ 90%</t>
         </is>
       </c>
       <c r="L107" s="30" t="inlineStr">
@@ -11054,21 +11054,19 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="O107" s="39" t="n"/>
-      <c r="P107" s="39" t="n"/>
-      <c r="Q107" s="39" t="n"/>
-      <c r="R107" s="39" t="n"/>
-      <c r="S107" s="39" t="n"/>
-      <c r="T107" s="39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U107" s="39" t="n"/>
-      <c r="V107" s="39" t="n"/>
-      <c r="W107" s="39" t="n"/>
-      <c r="X107" s="39" t="n"/>
-      <c r="Y107" s="39" t="n"/>
-      <c r="Z107" s="39" t="n"/>
-      <c r="AA107" s="40">
+      <c r="O107" s="36" t="n"/>
+      <c r="P107" s="36" t="n"/>
+      <c r="Q107" s="36" t="n"/>
+      <c r="R107" s="36" t="n"/>
+      <c r="S107" s="36" t="n"/>
+      <c r="T107" s="36" t="n"/>
+      <c r="U107" s="36" t="n"/>
+      <c r="V107" s="36" t="n"/>
+      <c r="W107" s="36" t="n"/>
+      <c r="X107" s="36" t="n"/>
+      <c r="Y107" s="36" t="n"/>
+      <c r="Z107" s="36" t="n"/>
+      <c r="AA107" s="37">
         <f>IF($G107="SUM",IF(COUNT($O107:$Z107)=0,"",SUM($O107:$Z107)),IF($G107="AVG",IFERROR(AVERAGE($O107:$Z107),""),IF($G107="LAST",IFERROR(LOOKUP(2,1/($O107:$Z107&lt;&gt;""),$O107:$Z107),""),"")))</f>
         <v/>
       </c>
@@ -11092,17 +11090,17 @@
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>أداء المشاريع</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>D365 FNO — المرحلة الثانية</t>
+          <t>نسبة الالتزام بميزانية المشاريع</t>
         </is>
       </c>
       <c r="E108" s="25" t="inlineStr">
         <is>
-          <t>وحدة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F108" s="25" t="inlineStr">
@@ -11112,7 +11110,7 @@
       </c>
       <c r="G108" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="H108" s="26" t="inlineStr">
@@ -11121,14 +11119,14 @@
         </is>
       </c>
       <c r="I108" s="27" t="n">
-        <v>0.03175</v>
-      </c>
-      <c r="J108" s="28" t="n">
-        <v>4</v>
+        <v>0.1</v>
+      </c>
+      <c r="J108" s="27" t="n">
+        <v>0.95</v>
       </c>
       <c r="K108" s="29" t="inlineStr">
         <is>
-          <t>4 وحدات</t>
+          <t>≥ 95%</t>
         </is>
       </c>
       <c r="L108" s="30" t="inlineStr">
@@ -11146,21 +11144,19 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="O108" s="32" t="n"/>
-      <c r="P108" s="32" t="n"/>
-      <c r="Q108" s="32" t="n"/>
-      <c r="R108" s="32" t="n"/>
-      <c r="S108" s="32" t="n"/>
-      <c r="T108" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" s="32" t="n"/>
-      <c r="V108" s="32" t="n"/>
-      <c r="W108" s="32" t="n"/>
-      <c r="X108" s="32" t="n"/>
-      <c r="Y108" s="32" t="n"/>
-      <c r="Z108" s="32" t="n"/>
-      <c r="AA108" s="33">
+      <c r="O108" s="36" t="n"/>
+      <c r="P108" s="36" t="n"/>
+      <c r="Q108" s="36" t="n"/>
+      <c r="R108" s="36" t="n"/>
+      <c r="S108" s="36" t="n"/>
+      <c r="T108" s="36" t="n"/>
+      <c r="U108" s="36" t="n"/>
+      <c r="V108" s="36" t="n"/>
+      <c r="W108" s="36" t="n"/>
+      <c r="X108" s="36" t="n"/>
+      <c r="Y108" s="36" t="n"/>
+      <c r="Z108" s="36" t="n"/>
+      <c r="AA108" s="37">
         <f>IF($G108="SUM",IF(COUNT($O108:$Z108)=0,"",SUM($O108:$Z108)),IF($G108="AVG",IFERROR(AVERAGE($O108:$Z108),""),IF($G108="LAST",IFERROR(LOOKUP(2,1/($O108:$Z108&lt;&gt;""),$O108:$Z108),""),"")))</f>
         <v/>
       </c>
@@ -11184,17 +11180,17 @@
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>أداء المشاريع</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>D365 FNO — المرحلة الثالثة</t>
+          <t>نسبة الالتزام بنطاق العمل</t>
         </is>
       </c>
       <c r="E109" s="25" t="inlineStr">
         <is>
-          <t>وحدة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F109" s="25" t="inlineStr">
@@ -11213,14 +11209,14 @@
         </is>
       </c>
       <c r="I109" s="27" t="n">
-        <v>0.03175</v>
-      </c>
-      <c r="J109" s="28" t="n">
-        <v>2</v>
+        <v>0.1</v>
+      </c>
+      <c r="J109" s="27" t="n">
+        <v>0.95</v>
       </c>
       <c r="K109" s="29" t="inlineStr">
         <is>
-          <t>وحدتان</t>
+          <t>≥ 95%</t>
         </is>
       </c>
       <c r="L109" s="30" t="inlineStr">
@@ -11238,21 +11234,19 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="O109" s="32" t="n"/>
-      <c r="P109" s="32" t="n"/>
-      <c r="Q109" s="32" t="n"/>
-      <c r="R109" s="32" t="n"/>
-      <c r="S109" s="32" t="n"/>
-      <c r="T109" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U109" s="32" t="n"/>
-      <c r="V109" s="32" t="n"/>
-      <c r="W109" s="32" t="n"/>
-      <c r="X109" s="32" t="n"/>
-      <c r="Y109" s="32" t="n"/>
-      <c r="Z109" s="32" t="n"/>
-      <c r="AA109" s="33">
+      <c r="O109" s="36" t="n"/>
+      <c r="P109" s="36" t="n"/>
+      <c r="Q109" s="36" t="n"/>
+      <c r="R109" s="36" t="n"/>
+      <c r="S109" s="36" t="n"/>
+      <c r="T109" s="36" t="n"/>
+      <c r="U109" s="36" t="n"/>
+      <c r="V109" s="36" t="n"/>
+      <c r="W109" s="36" t="n"/>
+      <c r="X109" s="36" t="n"/>
+      <c r="Y109" s="36" t="n"/>
+      <c r="Z109" s="36" t="n"/>
+      <c r="AA109" s="37">
         <f>IF($G109="SUM",IF(COUNT($O109:$Z109)=0,"",SUM($O109:$Z109)),IF($G109="AVG",IFERROR(AVERAGE($O109:$Z109),""),IF($G109="LAST",IFERROR(LOOKUP(2,1/($O109:$Z109&lt;&gt;""),$O109:$Z109),""),"")))</f>
         <v/>
       </c>
@@ -11276,17 +11270,17 @@
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>الكفاءة التشغيلية</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>تطبيق الامتياز مع واثق</t>
+          <t>نسبة تفعيل الأنظمة الأساسية بالمحطات</t>
         </is>
       </c>
       <c r="E110" s="25" t="inlineStr">
         <is>
-          <t>تطبيق</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F110" s="25" t="inlineStr">
@@ -11301,28 +11295,28 @@
       </c>
       <c r="H110" s="26" t="inlineStr">
         <is>
-          <t>🟠 مهم</t>
+          <t>🔴 رئيسي</t>
         </is>
       </c>
       <c r="I110" s="27" t="n">
-        <v>0.03175</v>
-      </c>
-      <c r="J110" s="28" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J110" s="27" t="n">
         <v>1</v>
       </c>
       <c r="K110" s="29" t="inlineStr">
         <is>
-          <t>تطبيق واحد</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="L110" s="30" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="M110" s="31" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="N110" s="26" t="inlineStr">
@@ -11330,21 +11324,21 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="O110" s="32" t="n"/>
-      <c r="P110" s="32" t="n"/>
-      <c r="Q110" s="32" t="n"/>
-      <c r="R110" s="32" t="n"/>
-      <c r="S110" s="32" t="n"/>
-      <c r="T110" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U110" s="32" t="n"/>
-      <c r="V110" s="32" t="n"/>
-      <c r="W110" s="32" t="n"/>
-      <c r="X110" s="32" t="n"/>
-      <c r="Y110" s="32" t="n"/>
-      <c r="Z110" s="32" t="n"/>
-      <c r="AA110" s="33">
+      <c r="O110" s="36" t="n"/>
+      <c r="P110" s="36" t="n"/>
+      <c r="Q110" s="36" t="n"/>
+      <c r="R110" s="36" t="n"/>
+      <c r="S110" s="36" t="n"/>
+      <c r="T110" s="36" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U110" s="36" t="n"/>
+      <c r="V110" s="36" t="n"/>
+      <c r="W110" s="36" t="n"/>
+      <c r="X110" s="36" t="n"/>
+      <c r="Y110" s="36" t="n"/>
+      <c r="Z110" s="36" t="n"/>
+      <c r="AA110" s="37">
         <f>IF($G110="SUM",IF(COUNT($O110:$Z110)=0,"",SUM($O110:$Z110)),IF($G110="AVG",IFERROR(AVERAGE($O110:$Z110),""),IF($G110="LAST",IFERROR(LOOKUP(2,1/($O110:$Z110&lt;&gt;""),$O110:$Z110),""),"")))</f>
         <v/>
       </c>
@@ -11368,17 +11362,17 @@
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>الكفاءة التشغيلية</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>ربط المحطات بوزارة الطاقة (ATJ)</t>
+          <t>متوسط جاهزية أنظمة المركز الرئيسي (Uptime)</t>
         </is>
       </c>
       <c r="E111" s="25" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F111" s="25" t="inlineStr">
@@ -11388,7 +11382,7 @@
       </c>
       <c r="G111" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="H111" s="26" t="inlineStr">
@@ -11397,24 +11391,24 @@
         </is>
       </c>
       <c r="I111" s="27" t="n">
-        <v>0.04762</v>
-      </c>
-      <c r="J111" s="28" t="n">
-        <v>164</v>
+        <v>0.15</v>
+      </c>
+      <c r="J111" s="27" t="n">
+        <v>0.99</v>
       </c>
       <c r="K111" s="29" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>≥ 99%</t>
         </is>
       </c>
       <c r="L111" s="30" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="M111" s="31" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="N111" s="26" t="inlineStr">
@@ -11422,21 +11416,21 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="O111" s="32" t="n"/>
-      <c r="P111" s="32" t="n"/>
-      <c r="Q111" s="32" t="n"/>
-      <c r="R111" s="32" t="n"/>
-      <c r="S111" s="32" t="n"/>
-      <c r="T111" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U111" s="32" t="n"/>
-      <c r="V111" s="32" t="n"/>
-      <c r="W111" s="32" t="n"/>
-      <c r="X111" s="32" t="n"/>
-      <c r="Y111" s="32" t="n"/>
-      <c r="Z111" s="32" t="n"/>
-      <c r="AA111" s="33">
+      <c r="O111" s="36" t="n"/>
+      <c r="P111" s="36" t="n"/>
+      <c r="Q111" s="36" t="n"/>
+      <c r="R111" s="36" t="n"/>
+      <c r="S111" s="36" t="n"/>
+      <c r="T111" s="36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="U111" s="36" t="n"/>
+      <c r="V111" s="36" t="n"/>
+      <c r="W111" s="36" t="n"/>
+      <c r="X111" s="36" t="n"/>
+      <c r="Y111" s="36" t="n"/>
+      <c r="Z111" s="36" t="n"/>
+      <c r="AA111" s="37">
         <f>IF($G111="SUM",IF(COUNT($O111:$Z111)=0,"",SUM($O111:$Z111)),IF($G111="AVG",IFERROR(AVERAGE($O111:$Z111),""),IF($G111="LAST",IFERROR(LOOKUP(2,1/($O111:$Z111&lt;&gt;""),$O111:$Z111),""),"")))</f>
         <v/>
       </c>
@@ -11460,17 +11454,17 @@
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>الكفاءة التشغيلية</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>ربط الكاميرات بالمركز الرئيسي</t>
+          <t>نسبة الامتثال للأمن السيبراني</t>
         </is>
       </c>
       <c r="E112" s="25" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F112" s="25" t="inlineStr">
@@ -11489,24 +11483,24 @@
         </is>
       </c>
       <c r="I112" s="27" t="n">
-        <v>0.03175</v>
-      </c>
-      <c r="J112" s="28" t="n">
-        <v>164</v>
+        <v>0.1</v>
+      </c>
+      <c r="J112" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="K112" s="29" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="L112" s="30" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="M112" s="31" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="N112" s="26" t="inlineStr">
@@ -11514,21 +11508,21 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="O112" s="32" t="n"/>
-      <c r="P112" s="32" t="n"/>
-      <c r="Q112" s="32" t="n"/>
-      <c r="R112" s="32" t="n"/>
-      <c r="S112" s="32" t="n"/>
-      <c r="T112" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U112" s="32" t="n"/>
-      <c r="V112" s="32" t="n"/>
-      <c r="W112" s="32" t="n"/>
-      <c r="X112" s="32" t="n"/>
-      <c r="Y112" s="32" t="n"/>
-      <c r="Z112" s="32" t="n"/>
-      <c r="AA112" s="33">
+      <c r="O112" s="36" t="n"/>
+      <c r="P112" s="36" t="n"/>
+      <c r="Q112" s="36" t="n"/>
+      <c r="R112" s="36" t="n"/>
+      <c r="S112" s="36" t="n"/>
+      <c r="T112" s="36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U112" s="36" t="n"/>
+      <c r="V112" s="36" t="n"/>
+      <c r="W112" s="36" t="n"/>
+      <c r="X112" s="36" t="n"/>
+      <c r="Y112" s="36" t="n"/>
+      <c r="Z112" s="36" t="n"/>
+      <c r="AA112" s="37">
         <f>IF($G112="SUM",IF(COUNT($O112:$Z112)=0,"",SUM($O112:$Z112)),IF($G112="AVG",IFERROR(AVERAGE($O112:$Z112),""),IF($G112="LAST",IFERROR(LOOKUP(2,1/($O112:$Z112&lt;&gt;""),$O112:$Z112),""),"")))</f>
         <v/>
       </c>
@@ -11552,53 +11546,53 @@
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>الكفاءة التشغيلية</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>تطبيق الولاء (تانكي) في المحطات</t>
+          <t>متوسط زمن استجابة الدعم الفني</t>
         </is>
       </c>
       <c r="E113" s="25" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>ساعة</t>
         </is>
       </c>
       <c r="F113" s="25" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="G113" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="H113" s="26" t="inlineStr">
         <is>
-          <t>🔴 رئيسي</t>
+          <t>🟠 مهم</t>
         </is>
       </c>
       <c r="I113" s="27" t="n">
-        <v>0.04762</v>
-      </c>
-      <c r="J113" s="28" t="n">
-        <v>164</v>
+        <v>0.1</v>
+      </c>
+      <c r="J113" s="38" t="n">
+        <v>1</v>
       </c>
       <c r="K113" s="29" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>≤ ساعة</t>
         </is>
       </c>
       <c r="L113" s="30" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="M113" s="31" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="N113" s="26" t="inlineStr">
@@ -11606,21 +11600,21 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="O113" s="32" t="n"/>
-      <c r="P113" s="32" t="n"/>
-      <c r="Q113" s="32" t="n"/>
-      <c r="R113" s="32" t="n"/>
-      <c r="S113" s="32" t="n"/>
-      <c r="T113" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U113" s="32" t="n"/>
-      <c r="V113" s="32" t="n"/>
-      <c r="W113" s="32" t="n"/>
-      <c r="X113" s="32" t="n"/>
-      <c r="Y113" s="32" t="n"/>
-      <c r="Z113" s="32" t="n"/>
-      <c r="AA113" s="33">
+      <c r="O113" s="39" t="n"/>
+      <c r="P113" s="39" t="n"/>
+      <c r="Q113" s="39" t="n"/>
+      <c r="R113" s="39" t="n"/>
+      <c r="S113" s="39" t="n"/>
+      <c r="T113" s="39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U113" s="39" t="n"/>
+      <c r="V113" s="39" t="n"/>
+      <c r="W113" s="39" t="n"/>
+      <c r="X113" s="39" t="n"/>
+      <c r="Y113" s="39" t="n"/>
+      <c r="Z113" s="39" t="n"/>
+      <c r="AA113" s="40">
         <f>IF($G113="SUM",IF(COUNT($O113:$Z113)=0,"",SUM($O113:$Z113)),IF($G113="AVG",IFERROR(AVERAGE($O113:$Z113),""),IF($G113="LAST",IFERROR(LOOKUP(2,1/($O113:$Z113&lt;&gt;""),$O113:$Z113),""),"")))</f>
         <v/>
       </c>
@@ -11644,17 +11638,17 @@
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>الكفاءة التشغيلية</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>منصة Tatin السحابية</t>
+          <t>نسبة التكامل الرقمي (ERP/واثق/الولاء)</t>
         </is>
       </c>
       <c r="E114" s="25" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F114" s="25" t="inlineStr">
@@ -11673,46 +11667,46 @@
         </is>
       </c>
       <c r="I114" s="27" t="n">
-        <v>0.03175</v>
-      </c>
-      <c r="J114" s="28" t="n">
-        <v>164</v>
+        <v>0.1</v>
+      </c>
+      <c r="J114" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="K114" s="29" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="L114" s="30" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="M114" s="31" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="N114" s="26" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O114" s="32" t="n"/>
-      <c r="P114" s="32" t="n"/>
-      <c r="Q114" s="32" t="n"/>
-      <c r="R114" s="32" t="n"/>
-      <c r="S114" s="32" t="n"/>
-      <c r="T114" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U114" s="32" t="n"/>
-      <c r="V114" s="32" t="n"/>
-      <c r="W114" s="32" t="n"/>
-      <c r="X114" s="32" t="n"/>
-      <c r="Y114" s="32" t="n"/>
-      <c r="Z114" s="32" t="n"/>
-      <c r="AA114" s="33">
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+      <c r="O114" s="36" t="n"/>
+      <c r="P114" s="36" t="n"/>
+      <c r="Q114" s="36" t="n"/>
+      <c r="R114" s="36" t="n"/>
+      <c r="S114" s="36" t="n"/>
+      <c r="T114" s="36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U114" s="36" t="n"/>
+      <c r="V114" s="36" t="n"/>
+      <c r="W114" s="36" t="n"/>
+      <c r="X114" s="36" t="n"/>
+      <c r="Y114" s="36" t="n"/>
+      <c r="Z114" s="36" t="n"/>
+      <c r="AA114" s="37">
         <f>IF($G114="SUM",IF(COUNT($O114:$Z114)=0,"",SUM($O114:$Z114)),IF($G114="AVG",IFERROR(AVERAGE($O114:$Z114),""),IF($G114="LAST",IFERROR(LOOKUP(2,1/($O114:$Z114&lt;&gt;""),$O114:$Z114),""),"")))</f>
         <v/>
       </c>
@@ -11731,22 +11725,22 @@
       </c>
       <c r="B115" s="21" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>التوظيف والتوطين</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>إدارة العمليات بالذكاء الاصطناعي</t>
+          <t>نسبة السعودة / التوطين</t>
         </is>
       </c>
       <c r="E115" s="25" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F115" s="25" t="inlineStr">
@@ -11765,46 +11759,42 @@
         </is>
       </c>
       <c r="I115" s="27" t="n">
-        <v>0.03175</v>
-      </c>
-      <c r="J115" s="28" t="n">
-        <v>164</v>
-      </c>
+        <v>0.05405</v>
+      </c>
+      <c r="J115" s="25" t="inlineStr"/>
       <c r="K115" s="29" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>أخضر مرتفع (حسب الوزارة)</t>
         </is>
       </c>
       <c r="L115" s="30" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="M115" s="31" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="N115" s="26" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O115" s="32" t="n"/>
-      <c r="P115" s="32" t="n"/>
-      <c r="Q115" s="32" t="n"/>
-      <c r="R115" s="32" t="n"/>
-      <c r="S115" s="32" t="n"/>
-      <c r="T115" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" s="32" t="n"/>
-      <c r="V115" s="32" t="n"/>
-      <c r="W115" s="32" t="n"/>
-      <c r="X115" s="32" t="n"/>
-      <c r="Y115" s="32" t="n"/>
-      <c r="Z115" s="32" t="n"/>
-      <c r="AA115" s="33">
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+      <c r="O115" s="36" t="n"/>
+      <c r="P115" s="36" t="n"/>
+      <c r="Q115" s="36" t="n"/>
+      <c r="R115" s="36" t="n"/>
+      <c r="S115" s="36" t="n"/>
+      <c r="T115" s="36" t="n"/>
+      <c r="U115" s="36" t="n"/>
+      <c r="V115" s="36" t="n"/>
+      <c r="W115" s="36" t="n"/>
+      <c r="X115" s="36" t="n"/>
+      <c r="Y115" s="36" t="n"/>
+      <c r="Z115" s="36" t="n"/>
+      <c r="AA115" s="37">
         <f>IF($G115="SUM",IF(COUNT($O115:$Z115)=0,"",SUM($O115:$Z115)),IF($G115="AVG",IFERROR(AVERAGE($O115:$Z115),""),IF($G115="LAST",IFERROR(LOOKUP(2,1/($O115:$Z115&lt;&gt;""),$O115:$Z115),""),"")))</f>
         <v/>
       </c>
@@ -11823,22 +11813,22 @@
       </c>
       <c r="B116" s="21" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>الكفاءة التشغيلية</t>
+          <t>التوظيف والتوطين</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>جاهزية أتمتة المحطات (Forecourt)</t>
+          <t>الارتقاء بآليات اختيار المرشحين</t>
         </is>
       </c>
       <c r="E116" s="25" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F116" s="25" t="inlineStr">
@@ -11853,18 +11843,18 @@
       </c>
       <c r="H116" s="26" t="inlineStr">
         <is>
-          <t>🔴 رئيسي</t>
+          <t>🟠 مهم</t>
         </is>
       </c>
       <c r="I116" s="27" t="n">
-        <v>0.04762</v>
-      </c>
-      <c r="J116" s="28" t="n">
-        <v>164</v>
+        <v>0.05405</v>
+      </c>
+      <c r="J116" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="K116" s="29" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="L116" s="30" t="inlineStr">
@@ -11874,29 +11864,27 @@
       </c>
       <c r="M116" s="31" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="N116" s="26" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
-        </is>
-      </c>
-      <c r="O116" s="32" t="n"/>
-      <c r="P116" s="32" t="n"/>
-      <c r="Q116" s="32" t="n"/>
-      <c r="R116" s="32" t="n"/>
-      <c r="S116" s="32" t="n"/>
-      <c r="T116" s="32" t="n">
-        <v>59</v>
-      </c>
-      <c r="U116" s="32" t="n"/>
-      <c r="V116" s="32" t="n"/>
-      <c r="W116" s="32" t="n"/>
-      <c r="X116" s="32" t="n"/>
-      <c r="Y116" s="32" t="n"/>
-      <c r="Z116" s="32" t="n"/>
-      <c r="AA116" s="33">
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="O116" s="36" t="n"/>
+      <c r="P116" s="36" t="n"/>
+      <c r="Q116" s="36" t="n"/>
+      <c r="R116" s="36" t="n"/>
+      <c r="S116" s="36" t="n"/>
+      <c r="T116" s="36" t="n"/>
+      <c r="U116" s="36" t="n"/>
+      <c r="V116" s="36" t="n"/>
+      <c r="W116" s="36" t="n"/>
+      <c r="X116" s="36" t="n"/>
+      <c r="Y116" s="36" t="n"/>
+      <c r="Z116" s="36" t="n"/>
+      <c r="AA116" s="37">
         <f>IF($G116="SUM",IF(COUNT($O116:$Z116)=0,"",SUM($O116:$Z116)),IF($G116="AVG",IFERROR(AVERAGE($O116:$Z116),""),IF($G116="LAST",IFERROR(LOOKUP(2,1/($O116:$Z116&lt;&gt;""),$O116:$Z116),""),"")))</f>
         <v/>
       </c>
@@ -11915,22 +11903,22 @@
       </c>
       <c r="B117" s="21" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>الكفاءة التشغيلية</t>
+          <t>التوظيف والتوطين</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>جاهزية اتصال الشبكة بالمحطات</t>
+          <t>نسبة شغل الشواغر خلال 30 يوم</t>
         </is>
       </c>
       <c r="E117" s="25" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F117" s="25" t="inlineStr">
@@ -11940,23 +11928,23 @@
       </c>
       <c r="G117" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="H117" s="26" t="inlineStr">
         <is>
-          <t>🔴 رئيسي</t>
+          <t>🟠 مهم</t>
         </is>
       </c>
       <c r="I117" s="27" t="n">
-        <v>0.04762</v>
-      </c>
-      <c r="J117" s="28" t="n">
-        <v>164</v>
+        <v>0.05405</v>
+      </c>
+      <c r="J117" s="27" t="n">
+        <v>0.85</v>
       </c>
       <c r="K117" s="29" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>≥ 85%</t>
         </is>
       </c>
       <c r="L117" s="30" t="inlineStr">
@@ -11966,7 +11954,7 @@
       </c>
       <c r="M117" s="31" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="N117" s="26" t="inlineStr">
@@ -11974,21 +11962,19 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="O117" s="32" t="n"/>
-      <c r="P117" s="32" t="n"/>
-      <c r="Q117" s="32" t="n"/>
-      <c r="R117" s="32" t="n"/>
-      <c r="S117" s="32" t="n"/>
-      <c r="T117" s="32" t="n">
-        <v>59</v>
-      </c>
-      <c r="U117" s="32" t="n"/>
-      <c r="V117" s="32" t="n"/>
-      <c r="W117" s="32" t="n"/>
-      <c r="X117" s="32" t="n"/>
-      <c r="Y117" s="32" t="n"/>
-      <c r="Z117" s="32" t="n"/>
-      <c r="AA117" s="33">
+      <c r="O117" s="36" t="n"/>
+      <c r="P117" s="36" t="n"/>
+      <c r="Q117" s="36" t="n"/>
+      <c r="R117" s="36" t="n"/>
+      <c r="S117" s="36" t="n"/>
+      <c r="T117" s="36" t="n"/>
+      <c r="U117" s="36" t="n"/>
+      <c r="V117" s="36" t="n"/>
+      <c r="W117" s="36" t="n"/>
+      <c r="X117" s="36" t="n"/>
+      <c r="Y117" s="36" t="n"/>
+      <c r="Z117" s="36" t="n"/>
+      <c r="AA117" s="37">
         <f>IF($G117="SUM",IF(COUNT($O117:$Z117)=0,"",SUM($O117:$Z117)),IF($G117="AVG",IFERROR(AVERAGE($O117:$Z117),""),IF($G117="LAST",IFERROR(LOOKUP(2,1/($O117:$Z117&lt;&gt;""),$O117:$Z117),""),"")))</f>
         <v/>
       </c>
@@ -12007,22 +11993,22 @@
       </c>
       <c r="B118" s="21" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>الكفاءة التشغيلية</t>
+          <t>الاستبقاء</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>جاهزية نقاط البيع والمدفوعات (POS)</t>
+          <t>معدل استبقاء الموظفين (Retention)</t>
         </is>
       </c>
       <c r="E118" s="25" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F118" s="25" t="inlineStr">
@@ -12041,14 +12027,14 @@
         </is>
       </c>
       <c r="I118" s="27" t="n">
-        <v>0.04762</v>
-      </c>
-      <c r="J118" s="28" t="n">
-        <v>164</v>
+        <v>0.08108</v>
+      </c>
+      <c r="J118" s="27" t="n">
+        <v>0.9</v>
       </c>
       <c r="K118" s="29" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>≥ 90%</t>
         </is>
       </c>
       <c r="L118" s="30" t="inlineStr">
@@ -12058,29 +12044,27 @@
       </c>
       <c r="M118" s="31" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="N118" s="26" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O118" s="32" t="n"/>
-      <c r="P118" s="32" t="n"/>
-      <c r="Q118" s="32" t="n"/>
-      <c r="R118" s="32" t="n"/>
-      <c r="S118" s="32" t="n"/>
-      <c r="T118" s="32" t="n">
-        <v>59</v>
-      </c>
-      <c r="U118" s="32" t="n"/>
-      <c r="V118" s="32" t="n"/>
-      <c r="W118" s="32" t="n"/>
-      <c r="X118" s="32" t="n"/>
-      <c r="Y118" s="32" t="n"/>
-      <c r="Z118" s="32" t="n"/>
-      <c r="AA118" s="33">
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+      <c r="O118" s="36" t="n"/>
+      <c r="P118" s="36" t="n"/>
+      <c r="Q118" s="36" t="n"/>
+      <c r="R118" s="36" t="n"/>
+      <c r="S118" s="36" t="n"/>
+      <c r="T118" s="36" t="n"/>
+      <c r="U118" s="36" t="n"/>
+      <c r="V118" s="36" t="n"/>
+      <c r="W118" s="36" t="n"/>
+      <c r="X118" s="36" t="n"/>
+      <c r="Y118" s="36" t="n"/>
+      <c r="Z118" s="36" t="n"/>
+      <c r="AA118" s="37">
         <f>IF($G118="SUM",IF(COUNT($O118:$Z118)=0,"",SUM($O118:$Z118)),IF($G118="AVG",IFERROR(AVERAGE($O118:$Z118),""),IF($G118="LAST",IFERROR(LOOKUP(2,1/($O118:$Z118&lt;&gt;""),$O118:$Z118),""),"")))</f>
         <v/>
       </c>
@@ -12099,48 +12083,48 @@
       </c>
       <c r="B119" s="21" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>الكفاءة التشغيلية</t>
+          <t>الاستبقاء</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>جاهزية نظام الكاميرات (CCTV)</t>
+          <t>معدل دوران الموظفين (Turnover)</t>
         </is>
       </c>
       <c r="E119" s="25" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F119" s="25" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="G119" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="H119" s="26" t="inlineStr">
         <is>
-          <t>🔴 رئيسي</t>
+          <t>🟠 مهم</t>
         </is>
       </c>
       <c r="I119" s="27" t="n">
-        <v>0.04762</v>
-      </c>
-      <c r="J119" s="28" t="n">
-        <v>164</v>
+        <v>0.05405</v>
+      </c>
+      <c r="J119" s="27" t="n">
+        <v>0.1</v>
       </c>
       <c r="K119" s="29" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>≤ 10%</t>
         </is>
       </c>
       <c r="L119" s="30" t="inlineStr">
@@ -12150,29 +12134,27 @@
       </c>
       <c r="M119" s="31" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="N119" s="26" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O119" s="32" t="n"/>
-      <c r="P119" s="32" t="n"/>
-      <c r="Q119" s="32" t="n"/>
-      <c r="R119" s="32" t="n"/>
-      <c r="S119" s="32" t="n"/>
-      <c r="T119" s="32" t="n">
-        <v>49</v>
-      </c>
-      <c r="U119" s="32" t="n"/>
-      <c r="V119" s="32" t="n"/>
-      <c r="W119" s="32" t="n"/>
-      <c r="X119" s="32" t="n"/>
-      <c r="Y119" s="32" t="n"/>
-      <c r="Z119" s="32" t="n"/>
-      <c r="AA119" s="33">
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+      <c r="O119" s="36" t="n"/>
+      <c r="P119" s="36" t="n"/>
+      <c r="Q119" s="36" t="n"/>
+      <c r="R119" s="36" t="n"/>
+      <c r="S119" s="36" t="n"/>
+      <c r="T119" s="36" t="n"/>
+      <c r="U119" s="36" t="n"/>
+      <c r="V119" s="36" t="n"/>
+      <c r="W119" s="36" t="n"/>
+      <c r="X119" s="36" t="n"/>
+      <c r="Y119" s="36" t="n"/>
+      <c r="Z119" s="36" t="n"/>
+      <c r="AA119" s="37">
         <f>IF($G119="SUM",IF(COUNT($O119:$Z119)=0,"",SUM($O119:$Z119)),IF($G119="AVG",IFERROR(AVERAGE($O119:$Z119),""),IF($G119="LAST",IFERROR(LOOKUP(2,1/($O119:$Z119&lt;&gt;""),$O119:$Z119),""),"")))</f>
         <v/>
       </c>
@@ -12191,22 +12173,22 @@
       </c>
       <c r="B120" s="21" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>الكفاءة التشغيلية</t>
+          <t>التدريب والتطوير</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>جاهزية الشبكة</t>
+          <t>عدد الدورات الإدارية المنعقدة</t>
         </is>
       </c>
       <c r="E120" s="25" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>دورة</t>
         </is>
       </c>
       <c r="F120" s="25" t="inlineStr">
@@ -12216,7 +12198,7 @@
       </c>
       <c r="G120" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="H120" s="26" t="inlineStr">
@@ -12225,14 +12207,14 @@
         </is>
       </c>
       <c r="I120" s="27" t="n">
-        <v>0.04762</v>
+        <v>0.08108</v>
       </c>
       <c r="J120" s="28" t="n">
-        <v>164</v>
+        <v>6</v>
       </c>
       <c r="K120" s="29" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>6 دورات</t>
         </is>
       </c>
       <c r="L120" s="30" t="inlineStr">
@@ -12242,7 +12224,7 @@
       </c>
       <c r="M120" s="31" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="N120" s="26" t="inlineStr">
@@ -12255,9 +12237,7 @@
       <c r="Q120" s="32" t="n"/>
       <c r="R120" s="32" t="n"/>
       <c r="S120" s="32" t="n"/>
-      <c r="T120" s="32" t="n">
-        <v>49</v>
-      </c>
+      <c r="T120" s="32" t="n"/>
       <c r="U120" s="32" t="n"/>
       <c r="V120" s="32" t="n"/>
       <c r="W120" s="32" t="n"/>
@@ -12283,22 +12263,22 @@
       </c>
       <c r="B121" s="21" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>الكفاءة التشغيلية</t>
+          <t>التدريب والتطوير</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>الامتثال للأمن السيبراني (المحطات)</t>
+          <t>متوسط ساعات التدريب لكل موظف</t>
         </is>
       </c>
       <c r="E121" s="25" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>ساعة</t>
         </is>
       </c>
       <c r="F121" s="25" t="inlineStr">
@@ -12308,23 +12288,23 @@
       </c>
       <c r="G121" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="H121" s="26" t="inlineStr">
         <is>
-          <t>🔴 رئيسي</t>
+          <t>🟠 مهم</t>
         </is>
       </c>
       <c r="I121" s="27" t="n">
-        <v>0.04762</v>
-      </c>
-      <c r="J121" s="28" t="n">
-        <v>164</v>
+        <v>0.05405</v>
+      </c>
+      <c r="J121" s="38" t="n">
+        <v>40</v>
       </c>
       <c r="K121" s="29" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>≥ 40 ساعة</t>
         </is>
       </c>
       <c r="L121" s="30" t="inlineStr">
@@ -12334,29 +12314,27 @@
       </c>
       <c r="M121" s="31" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="N121" s="26" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O121" s="32" t="n"/>
-      <c r="P121" s="32" t="n"/>
-      <c r="Q121" s="32" t="n"/>
-      <c r="R121" s="32" t="n"/>
-      <c r="S121" s="32" t="n"/>
-      <c r="T121" s="32" t="n">
-        <v>49</v>
-      </c>
-      <c r="U121" s="32" t="n"/>
-      <c r="V121" s="32" t="n"/>
-      <c r="W121" s="32" t="n"/>
-      <c r="X121" s="32" t="n"/>
-      <c r="Y121" s="32" t="n"/>
-      <c r="Z121" s="32" t="n"/>
-      <c r="AA121" s="33">
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+      <c r="O121" s="39" t="n"/>
+      <c r="P121" s="39" t="n"/>
+      <c r="Q121" s="39" t="n"/>
+      <c r="R121" s="39" t="n"/>
+      <c r="S121" s="39" t="n"/>
+      <c r="T121" s="39" t="n"/>
+      <c r="U121" s="39" t="n"/>
+      <c r="V121" s="39" t="n"/>
+      <c r="W121" s="39" t="n"/>
+      <c r="X121" s="39" t="n"/>
+      <c r="Y121" s="39" t="n"/>
+      <c r="Z121" s="39" t="n"/>
+      <c r="AA121" s="40">
         <f>IF($G121="SUM",IF(COUNT($O121:$Z121)=0,"",SUM($O121:$Z121)),IF($G121="AVG",IFERROR(AVERAGE($O121:$Z121),""),IF($G121="LAST",IFERROR(LOOKUP(2,1/($O121:$Z121&lt;&gt;""),$O121:$Z121),""),"")))</f>
         <v/>
       </c>
@@ -12375,48 +12353,48 @@
       </c>
       <c r="B122" s="21" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>الكفاءة التشغيلية</t>
+          <t>التدريب والتطوير</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>زمن استجابة الدعم الفني (المحطات)</t>
+          <t>نسبة الموظفين المشمولين بخطة تطوير</t>
         </is>
       </c>
       <c r="E122" s="25" t="inlineStr">
         <is>
-          <t>يوم</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F122" s="25" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="G122" s="25" t="inlineStr">
         <is>
-          <t>AVG</t>
+          <t>LAST</t>
         </is>
       </c>
       <c r="H122" s="26" t="inlineStr">
         <is>
-          <t>🔴 رئيسي</t>
+          <t>🟠 مهم</t>
         </is>
       </c>
       <c r="I122" s="27" t="n">
-        <v>0.04762</v>
-      </c>
-      <c r="J122" s="38" t="n">
-        <v>1</v>
+        <v>0.05405</v>
+      </c>
+      <c r="J122" s="27" t="n">
+        <v>0.8</v>
       </c>
       <c r="K122" s="29" t="inlineStr">
         <is>
-          <t>≤ يوم</t>
+          <t>≥ 80%</t>
         </is>
       </c>
       <c r="L122" s="30" t="inlineStr">
@@ -12426,29 +12404,27 @@
       </c>
       <c r="M122" s="31" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="N122" s="26" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O122" s="39" t="n"/>
-      <c r="P122" s="39" t="n"/>
-      <c r="Q122" s="39" t="n"/>
-      <c r="R122" s="39" t="n"/>
-      <c r="S122" s="39" t="n"/>
-      <c r="T122" s="39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U122" s="39" t="n"/>
-      <c r="V122" s="39" t="n"/>
-      <c r="W122" s="39" t="n"/>
-      <c r="X122" s="39" t="n"/>
-      <c r="Y122" s="39" t="n"/>
-      <c r="Z122" s="39" t="n"/>
-      <c r="AA122" s="40">
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+      <c r="O122" s="36" t="n"/>
+      <c r="P122" s="36" t="n"/>
+      <c r="Q122" s="36" t="n"/>
+      <c r="R122" s="36" t="n"/>
+      <c r="S122" s="36" t="n"/>
+      <c r="T122" s="36" t="n"/>
+      <c r="U122" s="36" t="n"/>
+      <c r="V122" s="36" t="n"/>
+      <c r="W122" s="36" t="n"/>
+      <c r="X122" s="36" t="n"/>
+      <c r="Y122" s="36" t="n"/>
+      <c r="Z122" s="36" t="n"/>
+      <c r="AA122" s="37">
         <f>IF($G122="SUM",IF(COUNT($O122:$Z122)=0,"",SUM($O122:$Z122)),IF($G122="AVG",IFERROR(AVERAGE($O122:$Z122),""),IF($G122="LAST",IFERROR(LOOKUP(2,1/($O122:$Z122&lt;&gt;""),$O122:$Z122),""),"")))</f>
         <v/>
       </c>
@@ -12467,22 +12443,22 @@
       </c>
       <c r="B123" s="21" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>الكفاءة التشغيلية</t>
+          <t>الرضا والثقافة</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>ERP والتكامل (المحطات)</t>
+          <t>مؤشر رضا الموظفين (eNPS)</t>
         </is>
       </c>
       <c r="E123" s="25" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>نقطة</t>
         </is>
       </c>
       <c r="F123" s="25" t="inlineStr">
@@ -12492,7 +12468,7 @@
       </c>
       <c r="G123" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="H123" s="26" t="inlineStr">
@@ -12501,14 +12477,14 @@
         </is>
       </c>
       <c r="I123" s="27" t="n">
-        <v>0.04762</v>
-      </c>
-      <c r="J123" s="28" t="n">
-        <v>164</v>
+        <v>0.08108</v>
+      </c>
+      <c r="J123" s="38" t="n">
+        <v>30</v>
       </c>
       <c r="K123" s="29" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>≥ 30</t>
         </is>
       </c>
       <c r="L123" s="30" t="inlineStr">
@@ -12518,29 +12494,27 @@
       </c>
       <c r="M123" s="31" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="N123" s="26" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O123" s="32" t="n"/>
-      <c r="P123" s="32" t="n"/>
-      <c r="Q123" s="32" t="n"/>
-      <c r="R123" s="32" t="n"/>
-      <c r="S123" s="32" t="n"/>
-      <c r="T123" s="32" t="n">
-        <v>49</v>
-      </c>
-      <c r="U123" s="32" t="n"/>
-      <c r="V123" s="32" t="n"/>
-      <c r="W123" s="32" t="n"/>
-      <c r="X123" s="32" t="n"/>
-      <c r="Y123" s="32" t="n"/>
-      <c r="Z123" s="32" t="n"/>
-      <c r="AA123" s="33">
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+      <c r="O123" s="39" t="n"/>
+      <c r="P123" s="39" t="n"/>
+      <c r="Q123" s="39" t="n"/>
+      <c r="R123" s="39" t="n"/>
+      <c r="S123" s="39" t="n"/>
+      <c r="T123" s="39" t="n"/>
+      <c r="U123" s="39" t="n"/>
+      <c r="V123" s="39" t="n"/>
+      <c r="W123" s="39" t="n"/>
+      <c r="X123" s="39" t="n"/>
+      <c r="Y123" s="39" t="n"/>
+      <c r="Z123" s="39" t="n"/>
+      <c r="AA123" s="40">
         <f>IF($G123="SUM",IF(COUNT($O123:$Z123)=0,"",SUM($O123:$Z123)),IF($G123="AVG",IFERROR(AVERAGE($O123:$Z123),""),IF($G123="LAST",IFERROR(LOOKUP(2,1/($O123:$Z123&lt;&gt;""),$O123:$Z123),""),"")))</f>
         <v/>
       </c>
@@ -12559,22 +12533,22 @@
       </c>
       <c r="B124" s="21" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>الكفاءة التشغيلية</t>
+          <t>الرضا والثقافة</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>تكامل واثق (المحطات)</t>
+          <t>تحسين مستوى الرضا الوظيفي</t>
         </is>
       </c>
       <c r="E124" s="25" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F124" s="25" t="inlineStr">
@@ -12584,7 +12558,7 @@
       </c>
       <c r="G124" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="H124" s="26" t="inlineStr">
@@ -12593,14 +12567,12 @@
         </is>
       </c>
       <c r="I124" s="27" t="n">
-        <v>0.04762</v>
-      </c>
-      <c r="J124" s="28" t="n">
-        <v>164</v>
-      </c>
+        <v>0.08108</v>
+      </c>
+      <c r="J124" s="25" t="inlineStr"/>
       <c r="K124" s="29" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>مستهدف سنوي</t>
         </is>
       </c>
       <c r="L124" s="30" t="inlineStr">
@@ -12610,29 +12582,27 @@
       </c>
       <c r="M124" s="31" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="N124" s="26" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O124" s="32" t="n"/>
-      <c r="P124" s="32" t="n"/>
-      <c r="Q124" s="32" t="n"/>
-      <c r="R124" s="32" t="n"/>
-      <c r="S124" s="32" t="n"/>
-      <c r="T124" s="32" t="n">
-        <v>49</v>
-      </c>
-      <c r="U124" s="32" t="n"/>
-      <c r="V124" s="32" t="n"/>
-      <c r="W124" s="32" t="n"/>
-      <c r="X124" s="32" t="n"/>
-      <c r="Y124" s="32" t="n"/>
-      <c r="Z124" s="32" t="n"/>
-      <c r="AA124" s="33">
+          <t>العملاء</t>
+        </is>
+      </c>
+      <c r="O124" s="36" t="n"/>
+      <c r="P124" s="36" t="n"/>
+      <c r="Q124" s="36" t="n"/>
+      <c r="R124" s="36" t="n"/>
+      <c r="S124" s="36" t="n"/>
+      <c r="T124" s="36" t="n"/>
+      <c r="U124" s="36" t="n"/>
+      <c r="V124" s="36" t="n"/>
+      <c r="W124" s="36" t="n"/>
+      <c r="X124" s="36" t="n"/>
+      <c r="Y124" s="36" t="n"/>
+      <c r="Z124" s="36" t="n"/>
+      <c r="AA124" s="37">
         <f>IF($G124="SUM",IF(COUNT($O124:$Z124)=0,"",SUM($O124:$Z124)),IF($G124="AVG",IFERROR(AVERAGE($O124:$Z124),""),IF($G124="LAST",IFERROR(LOOKUP(2,1/($O124:$Z124&lt;&gt;""),$O124:$Z124),""),"")))</f>
         <v/>
       </c>
@@ -12651,22 +12621,22 @@
       </c>
       <c r="B125" s="21" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>الكفاءة التشغيلية</t>
+          <t>الرضا والثقافة</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>تكامل تطبيق الولاء (المحطات)</t>
+          <t>ترسيخ القيم والثقافة المؤسسية</t>
         </is>
       </c>
       <c r="E125" s="25" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F125" s="25" t="inlineStr">
@@ -12681,18 +12651,18 @@
       </c>
       <c r="H125" s="26" t="inlineStr">
         <is>
-          <t>🔴 رئيسي</t>
+          <t>🟠 مهم</t>
         </is>
       </c>
       <c r="I125" s="27" t="n">
-        <v>0.04762</v>
-      </c>
-      <c r="J125" s="28" t="n">
-        <v>164</v>
+        <v>0.05405</v>
+      </c>
+      <c r="J125" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="K125" s="29" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="L125" s="30" t="inlineStr">
@@ -12702,7 +12672,7 @@
       </c>
       <c r="M125" s="31" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="N125" s="26" t="inlineStr">
@@ -12710,21 +12680,19 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="O125" s="32" t="n"/>
-      <c r="P125" s="32" t="n"/>
-      <c r="Q125" s="32" t="n"/>
-      <c r="R125" s="32" t="n"/>
-      <c r="S125" s="32" t="n"/>
-      <c r="T125" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U125" s="32" t="n"/>
-      <c r="V125" s="32" t="n"/>
-      <c r="W125" s="32" t="n"/>
-      <c r="X125" s="32" t="n"/>
-      <c r="Y125" s="32" t="n"/>
-      <c r="Z125" s="32" t="n"/>
-      <c r="AA125" s="33">
+      <c r="O125" s="36" t="n"/>
+      <c r="P125" s="36" t="n"/>
+      <c r="Q125" s="36" t="n"/>
+      <c r="R125" s="36" t="n"/>
+      <c r="S125" s="36" t="n"/>
+      <c r="T125" s="36" t="n"/>
+      <c r="U125" s="36" t="n"/>
+      <c r="V125" s="36" t="n"/>
+      <c r="W125" s="36" t="n"/>
+      <c r="X125" s="36" t="n"/>
+      <c r="Y125" s="36" t="n"/>
+      <c r="Z125" s="36" t="n"/>
+      <c r="AA125" s="37">
         <f>IF($G125="SUM",IF(COUNT($O125:$Z125)=0,"",SUM($O125:$Z125)),IF($G125="AVG",IFERROR(AVERAGE($O125:$Z125),""),IF($G125="LAST",IFERROR(LOOKUP(2,1/($O125:$Z125&lt;&gt;""),$O125:$Z125),""),"")))</f>
         <v/>
       </c>
@@ -12743,22 +12711,22 @@
       </c>
       <c r="B126" s="21" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>المركز الرئيسي</t>
+          <t>الأتمتة والتوثيق</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>جاهزية شبكة المركز الرئيسي</t>
+          <t>نسبة أتمتة عمليات الموارد البشرية</t>
         </is>
       </c>
       <c r="E126" s="25" t="inlineStr">
         <is>
-          <t>ساعة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F126" s="25" t="inlineStr">
@@ -12773,50 +12741,48 @@
       </c>
       <c r="H126" s="26" t="inlineStr">
         <is>
-          <t>🔴 رئيسي</t>
+          <t>🟠 مهم</t>
         </is>
       </c>
       <c r="I126" s="27" t="n">
-        <v>0.04762</v>
-      </c>
-      <c r="J126" s="28" t="n">
-        <v>24</v>
+        <v>0.05405</v>
+      </c>
+      <c r="J126" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="K126" s="29" t="inlineStr">
         <is>
-          <t>24 ساعة</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="L126" s="30" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>الابتكار</t>
         </is>
       </c>
       <c r="M126" s="31" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>التحول التقني</t>
         </is>
       </c>
       <c r="N126" s="26" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O126" s="32" t="n"/>
-      <c r="P126" s="32" t="n"/>
-      <c r="Q126" s="32" t="n"/>
-      <c r="R126" s="32" t="n"/>
-      <c r="S126" s="32" t="n"/>
-      <c r="T126" s="32" t="n">
-        <v>23</v>
-      </c>
-      <c r="U126" s="32" t="n"/>
-      <c r="V126" s="32" t="n"/>
-      <c r="W126" s="32" t="n"/>
-      <c r="X126" s="32" t="n"/>
-      <c r="Y126" s="32" t="n"/>
-      <c r="Z126" s="32" t="n"/>
-      <c r="AA126" s="33">
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+      <c r="O126" s="36" t="n"/>
+      <c r="P126" s="36" t="n"/>
+      <c r="Q126" s="36" t="n"/>
+      <c r="R126" s="36" t="n"/>
+      <c r="S126" s="36" t="n"/>
+      <c r="T126" s="36" t="n"/>
+      <c r="U126" s="36" t="n"/>
+      <c r="V126" s="36" t="n"/>
+      <c r="W126" s="36" t="n"/>
+      <c r="X126" s="36" t="n"/>
+      <c r="Y126" s="36" t="n"/>
+      <c r="Z126" s="36" t="n"/>
+      <c r="AA126" s="37">
         <f>IF($G126="SUM",IF(COUNT($O126:$Z126)=0,"",SUM($O126:$Z126)),IF($G126="AVG",IFERROR(AVERAGE($O126:$Z126),""),IF($G126="LAST",IFERROR(LOOKUP(2,1/($O126:$Z126&lt;&gt;""),$O126:$Z126),""),"")))</f>
         <v/>
       </c>
@@ -12835,22 +12801,22 @@
       </c>
       <c r="B127" s="21" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>المركز الرئيسي</t>
+          <t>الأتمتة والتوثيق</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>جاهزية تطبيقات المركز الرئيسي</t>
+          <t>نسبة توثيق أنظمة العمل</t>
         </is>
       </c>
       <c r="E127" s="25" t="inlineStr">
         <is>
-          <t>ساعة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F127" s="25" t="inlineStr">
@@ -12865,18 +12831,18 @@
       </c>
       <c r="H127" s="26" t="inlineStr">
         <is>
-          <t>🔴 رئيسي</t>
+          <t>🟡 متابعة</t>
         </is>
       </c>
       <c r="I127" s="27" t="n">
-        <v>0.04762</v>
-      </c>
-      <c r="J127" s="28" t="n">
-        <v>24</v>
+        <v>0.02703</v>
+      </c>
+      <c r="J127" s="27" t="n">
+        <v>0.8</v>
       </c>
       <c r="K127" s="29" t="inlineStr">
         <is>
-          <t>24 ساعة</t>
+          <t>≥ 80%</t>
         </is>
       </c>
       <c r="L127" s="30" t="inlineStr">
@@ -12894,21 +12860,19 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="O127" s="32" t="n"/>
-      <c r="P127" s="32" t="n"/>
-      <c r="Q127" s="32" t="n"/>
-      <c r="R127" s="32" t="n"/>
-      <c r="S127" s="32" t="n"/>
-      <c r="T127" s="32" t="n">
-        <v>20</v>
-      </c>
-      <c r="U127" s="32" t="n"/>
-      <c r="V127" s="32" t="n"/>
-      <c r="W127" s="32" t="n"/>
-      <c r="X127" s="32" t="n"/>
-      <c r="Y127" s="32" t="n"/>
-      <c r="Z127" s="32" t="n"/>
-      <c r="AA127" s="33">
+      <c r="O127" s="36" t="n"/>
+      <c r="P127" s="36" t="n"/>
+      <c r="Q127" s="36" t="n"/>
+      <c r="R127" s="36" t="n"/>
+      <c r="S127" s="36" t="n"/>
+      <c r="T127" s="36" t="n"/>
+      <c r="U127" s="36" t="n"/>
+      <c r="V127" s="36" t="n"/>
+      <c r="W127" s="36" t="n"/>
+      <c r="X127" s="36" t="n"/>
+      <c r="Y127" s="36" t="n"/>
+      <c r="Z127" s="36" t="n"/>
+      <c r="AA127" s="37">
         <f>IF($G127="SUM",IF(COUNT($O127:$Z127)=0,"",SUM($O127:$Z127)),IF($G127="AVG",IFERROR(AVERAGE($O127:$Z127),""),IF($G127="LAST",IFERROR(LOOKUP(2,1/($O127:$Z127&lt;&gt;""),$O127:$Z127),""),"")))</f>
         <v/>
       </c>
@@ -12927,32 +12891,32 @@
       </c>
       <c r="B128" s="21" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>المركز الرئيسي</t>
+          <t>الأتمتة والتوثيق</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>زمن استجابة الدعم (المركز)</t>
+          <t>ترسيخ الأنظمة الإدارية</t>
         </is>
       </c>
       <c r="E128" s="25" t="inlineStr">
         <is>
-          <t>ساعة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F128" s="25" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="G128" s="25" t="inlineStr">
         <is>
-          <t>AVG</t>
+          <t>LAST</t>
         </is>
       </c>
       <c r="H128" s="26" t="inlineStr">
@@ -12961,14 +12925,14 @@
         </is>
       </c>
       <c r="I128" s="27" t="n">
-        <v>0.03175</v>
-      </c>
-      <c r="J128" s="38" t="n">
-        <v>1</v>
+        <v>0.05405</v>
+      </c>
+      <c r="J128" s="27" t="n">
+        <v>0.8</v>
       </c>
       <c r="K128" s="29" t="inlineStr">
         <is>
-          <t>≤ ساعة</t>
+          <t>≥ 80%</t>
         </is>
       </c>
       <c r="L128" s="30" t="inlineStr">
@@ -12986,21 +12950,19 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="O128" s="39" t="n"/>
-      <c r="P128" s="39" t="n"/>
-      <c r="Q128" s="39" t="n"/>
-      <c r="R128" s="39" t="n"/>
-      <c r="S128" s="39" t="n"/>
-      <c r="T128" s="39" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U128" s="39" t="n"/>
-      <c r="V128" s="39" t="n"/>
-      <c r="W128" s="39" t="n"/>
-      <c r="X128" s="39" t="n"/>
-      <c r="Y128" s="39" t="n"/>
-      <c r="Z128" s="39" t="n"/>
-      <c r="AA128" s="40">
+      <c r="O128" s="36" t="n"/>
+      <c r="P128" s="36" t="n"/>
+      <c r="Q128" s="36" t="n"/>
+      <c r="R128" s="36" t="n"/>
+      <c r="S128" s="36" t="n"/>
+      <c r="T128" s="36" t="n"/>
+      <c r="U128" s="36" t="n"/>
+      <c r="V128" s="36" t="n"/>
+      <c r="W128" s="36" t="n"/>
+      <c r="X128" s="36" t="n"/>
+      <c r="Y128" s="36" t="n"/>
+      <c r="Z128" s="36" t="n"/>
+      <c r="AA128" s="37">
         <f>IF($G128="SUM",IF(COUNT($O128:$Z128)=0,"",SUM($O128:$Z128)),IF($G128="AVG",IFERROR(AVERAGE($O128:$Z128),""),IF($G128="LAST",IFERROR(LOOKUP(2,1/($O128:$Z128&lt;&gt;""),$O128:$Z128),""),"")))</f>
         <v/>
       </c>
@@ -13019,17 +12981,17 @@
       </c>
       <c r="B129" s="21" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>المركز الرئيسي</t>
+          <t>الهيكلة</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>الامتثال للأمن السيبراني (المركز)</t>
+          <t>اعتماد الهيكل التنظيمي</t>
         </is>
       </c>
       <c r="E129" s="25" t="inlineStr">
@@ -13053,7 +13015,7 @@
         </is>
       </c>
       <c r="I129" s="27" t="n">
-        <v>0.03175</v>
+        <v>0.05405</v>
       </c>
       <c r="J129" s="27" t="n">
         <v>1</v>
@@ -13083,9 +13045,7 @@
       <c r="Q129" s="36" t="n"/>
       <c r="R129" s="36" t="n"/>
       <c r="S129" s="36" t="n"/>
-      <c r="T129" s="36" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="T129" s="36" t="n"/>
       <c r="U129" s="36" t="n"/>
       <c r="V129" s="36" t="n"/>
       <c r="W129" s="36" t="n"/>
@@ -13116,12 +13076,12 @@
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>التوظيف والتوطين</t>
+          <t>الهيكلة</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>نسبة السعودة / التوطين</t>
+          <t>اكتمال الأوصاف الوظيفية (+KPI)</t>
         </is>
       </c>
       <c r="E130" s="25" t="inlineStr">
@@ -13147,10 +13107,12 @@
       <c r="I130" s="27" t="n">
         <v>0.05405</v>
       </c>
-      <c r="J130" s="25" t="inlineStr"/>
+      <c r="J130" s="27" t="n">
+        <v>1</v>
+      </c>
       <c r="K130" s="29" t="inlineStr">
         <is>
-          <t>أخضر مرتفع (حسب الوزارة)</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="L130" s="30" t="inlineStr">
@@ -13160,12 +13122,12 @@
       </c>
       <c r="M130" s="31" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="N130" s="26" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="O130" s="36" t="n"/>
@@ -13204,12 +13166,12 @@
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>التوظيف والتوطين</t>
+          <t>الأداء</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>الارتقاء بآليات اختيار المرشحين</t>
+          <t>نسبة إنجاز تقييمات الأداء في موعدها</t>
         </is>
       </c>
       <c r="E131" s="25" t="inlineStr">
@@ -13224,7 +13186,7 @@
       </c>
       <c r="G131" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="H131" s="26" t="inlineStr">
@@ -13289,22 +13251,22 @@
       </c>
       <c r="B132" s="21" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>التوظيف والتوطين</t>
+          <t>الإدارة العامة</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>نسبة شغل الشواغر خلال 30 يوم</t>
+          <t>الوصول الكلي (Total Reach)</t>
         </is>
       </c>
       <c r="E132" s="25" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>وصول</t>
         </is>
       </c>
       <c r="F132" s="25" t="inlineStr">
@@ -13314,53 +13276,55 @@
       </c>
       <c r="G132" s="25" t="inlineStr">
         <is>
-          <t>AVG</t>
+          <t>LAST</t>
         </is>
       </c>
       <c r="H132" s="26" t="inlineStr">
         <is>
-          <t>🟠 مهم</t>
+          <t>🔴 رئيسي</t>
         </is>
       </c>
       <c r="I132" s="27" t="n">
-        <v>0.05405</v>
-      </c>
-      <c r="J132" s="27" t="n">
-        <v>0.85</v>
+        <v>0.08333</v>
+      </c>
+      <c r="J132" s="28" t="n">
+        <v>50000000</v>
       </c>
       <c r="K132" s="29" t="inlineStr">
         <is>
-          <t>≥ 85%</t>
+          <t>50م وصول</t>
         </is>
       </c>
       <c r="L132" s="30" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>النمو</t>
         </is>
       </c>
       <c r="M132" s="31" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>زيادة وصول العملاء</t>
         </is>
       </c>
       <c r="N132" s="26" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O132" s="36" t="n"/>
-      <c r="P132" s="36" t="n"/>
-      <c r="Q132" s="36" t="n"/>
-      <c r="R132" s="36" t="n"/>
-      <c r="S132" s="36" t="n"/>
-      <c r="T132" s="36" t="n"/>
-      <c r="U132" s="36" t="n"/>
-      <c r="V132" s="36" t="n"/>
-      <c r="W132" s="36" t="n"/>
-      <c r="X132" s="36" t="n"/>
-      <c r="Y132" s="36" t="n"/>
-      <c r="Z132" s="36" t="n"/>
-      <c r="AA132" s="37">
+          <t>العملاء</t>
+        </is>
+      </c>
+      <c r="O132" s="32" t="n"/>
+      <c r="P132" s="32" t="n"/>
+      <c r="Q132" s="32" t="n"/>
+      <c r="R132" s="32" t="n"/>
+      <c r="S132" s="32" t="n"/>
+      <c r="T132" s="32" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="U132" s="32" t="n"/>
+      <c r="V132" s="32" t="n"/>
+      <c r="W132" s="32" t="n"/>
+      <c r="X132" s="32" t="n"/>
+      <c r="Y132" s="32" t="n"/>
+      <c r="Z132" s="32" t="n"/>
+      <c r="AA132" s="33">
         <f>IF($G132="SUM",IF(COUNT($O132:$Z132)=0,"",SUM($O132:$Z132)),IF($G132="AVG",IFERROR(AVERAGE($O132:$Z132),""),IF($G132="LAST",IFERROR(LOOKUP(2,1/($O132:$Z132&lt;&gt;""),$O132:$Z132),""),"")))</f>
         <v/>
       </c>
@@ -13379,22 +13343,22 @@
       </c>
       <c r="B133" s="21" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>الاستبقاء</t>
+          <t>الإدارة العامة</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>معدل استبقاء الموظفين (Retention)</t>
+          <t>عملاء تجاريون جدد</t>
         </is>
       </c>
       <c r="E133" s="25" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>عميل</t>
         </is>
       </c>
       <c r="F133" s="25" t="inlineStr">
@@ -13404,53 +13368,55 @@
       </c>
       <c r="G133" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="H133" s="26" t="inlineStr">
         <is>
-          <t>🔴 رئيسي</t>
+          <t>🟠 مهم</t>
         </is>
       </c>
       <c r="I133" s="27" t="n">
-        <v>0.08108</v>
-      </c>
-      <c r="J133" s="27" t="n">
-        <v>0.9</v>
+        <v>0.05556</v>
+      </c>
+      <c r="J133" s="28" t="n">
+        <v>200</v>
       </c>
       <c r="K133" s="29" t="inlineStr">
         <is>
-          <t>≥ 90%</t>
+          <t>200 عميل</t>
         </is>
       </c>
       <c r="L133" s="30" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>النمو</t>
         </is>
       </c>
       <c r="M133" s="31" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>زيادة وصول العملاء</t>
         </is>
       </c>
       <c r="N133" s="26" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
-        </is>
-      </c>
-      <c r="O133" s="36" t="n"/>
-      <c r="P133" s="36" t="n"/>
-      <c r="Q133" s="36" t="n"/>
-      <c r="R133" s="36" t="n"/>
-      <c r="S133" s="36" t="n"/>
-      <c r="T133" s="36" t="n"/>
-      <c r="U133" s="36" t="n"/>
-      <c r="V133" s="36" t="n"/>
-      <c r="W133" s="36" t="n"/>
-      <c r="X133" s="36" t="n"/>
-      <c r="Y133" s="36" t="n"/>
-      <c r="Z133" s="36" t="n"/>
-      <c r="AA133" s="37">
+          <t>العملاء</t>
+        </is>
+      </c>
+      <c r="O133" s="32" t="n"/>
+      <c r="P133" s="32" t="n"/>
+      <c r="Q133" s="32" t="n"/>
+      <c r="R133" s="32" t="n"/>
+      <c r="S133" s="32" t="n"/>
+      <c r="T133" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U133" s="32" t="n"/>
+      <c r="V133" s="32" t="n"/>
+      <c r="W133" s="32" t="n"/>
+      <c r="X133" s="32" t="n"/>
+      <c r="Y133" s="32" t="n"/>
+      <c r="Z133" s="32" t="n"/>
+      <c r="AA133" s="33">
         <f>IF($G133="SUM",IF(COUNT($O133:$Z133)=0,"",SUM($O133:$Z133)),IF($G133="AVG",IFERROR(AVERAGE($O133:$Z133),""),IF($G133="LAST",IFERROR(LOOKUP(2,1/($O133:$Z133&lt;&gt;""),$O133:$Z133),""),"")))</f>
         <v/>
       </c>
@@ -13469,78 +13435,80 @@
       </c>
       <c r="B134" s="21" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>الاستبقاء</t>
+          <t>الفريق الإبداعي</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>معدل دوران الموظفين (Turnover)</t>
+          <t>إجمالي المتابعين (كل المنصات)</t>
         </is>
       </c>
       <c r="E134" s="25" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>متابع</t>
         </is>
       </c>
       <c r="F134" s="25" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="G134" s="25" t="inlineStr">
         <is>
-          <t>AVG</t>
+          <t>LAST</t>
         </is>
       </c>
       <c r="H134" s="26" t="inlineStr">
         <is>
-          <t>🟠 مهم</t>
+          <t>🔴 رئيسي</t>
         </is>
       </c>
       <c r="I134" s="27" t="n">
-        <v>0.05405</v>
-      </c>
-      <c r="J134" s="27" t="n">
-        <v>0.1</v>
+        <v>0.08333</v>
+      </c>
+      <c r="J134" s="28" t="n">
+        <v>380000</v>
       </c>
       <c r="K134" s="29" t="inlineStr">
         <is>
-          <t>≤ 10%</t>
+          <t>380ك متابع</t>
         </is>
       </c>
       <c r="L134" s="30" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>النمو</t>
         </is>
       </c>
       <c r="M134" s="31" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>زيادة وصول العملاء</t>
         </is>
       </c>
       <c r="N134" s="26" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
-        </is>
-      </c>
-      <c r="O134" s="36" t="n"/>
-      <c r="P134" s="36" t="n"/>
-      <c r="Q134" s="36" t="n"/>
-      <c r="R134" s="36" t="n"/>
-      <c r="S134" s="36" t="n"/>
-      <c r="T134" s="36" t="n"/>
-      <c r="U134" s="36" t="n"/>
-      <c r="V134" s="36" t="n"/>
-      <c r="W134" s="36" t="n"/>
-      <c r="X134" s="36" t="n"/>
-      <c r="Y134" s="36" t="n"/>
-      <c r="Z134" s="36" t="n"/>
-      <c r="AA134" s="37">
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="O134" s="32" t="n"/>
+      <c r="P134" s="32" t="n"/>
+      <c r="Q134" s="32" t="n"/>
+      <c r="R134" s="32" t="n"/>
+      <c r="S134" s="32" t="n"/>
+      <c r="T134" s="32" t="n">
+        <v>253000</v>
+      </c>
+      <c r="U134" s="32" t="n"/>
+      <c r="V134" s="32" t="n"/>
+      <c r="W134" s="32" t="n"/>
+      <c r="X134" s="32" t="n"/>
+      <c r="Y134" s="32" t="n"/>
+      <c r="Z134" s="32" t="n"/>
+      <c r="AA134" s="33">
         <f>IF($G134="SUM",IF(COUNT($O134:$Z134)=0,"",SUM($O134:$Z134)),IF($G134="AVG",IFERROR(AVERAGE($O134:$Z134),""),IF($G134="LAST",IFERROR(LOOKUP(2,1/($O134:$Z134&lt;&gt;""),$O134:$Z134),""),"")))</f>
         <v/>
       </c>
@@ -13559,22 +13527,22 @@
       </c>
       <c r="B135" s="21" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>التدريب والتطوير</t>
+          <t>الفريق الإبداعي</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>عدد الدورات الإدارية المنعقدة</t>
+          <t>معدل التفاعل (Engagement)</t>
         </is>
       </c>
       <c r="E135" s="25" t="inlineStr">
         <is>
-          <t>دورة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F135" s="25" t="inlineStr">
@@ -13584,7 +13552,7 @@
       </c>
       <c r="G135" s="25" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="H135" s="26" t="inlineStr">
@@ -13593,24 +13561,24 @@
         </is>
       </c>
       <c r="I135" s="27" t="n">
-        <v>0.08108</v>
-      </c>
-      <c r="J135" s="28" t="n">
-        <v>6</v>
+        <v>0.08333</v>
+      </c>
+      <c r="J135" s="27" t="n">
+        <v>0.5</v>
       </c>
       <c r="K135" s="29" t="inlineStr">
         <is>
-          <t>6 دورات</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L135" s="30" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>النمو</t>
         </is>
       </c>
       <c r="M135" s="31" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>زيادة وصول العملاء</t>
         </is>
       </c>
       <c r="N135" s="26" t="inlineStr">
@@ -13618,19 +13586,21 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="O135" s="32" t="n"/>
-      <c r="P135" s="32" t="n"/>
-      <c r="Q135" s="32" t="n"/>
-      <c r="R135" s="32" t="n"/>
-      <c r="S135" s="32" t="n"/>
-      <c r="T135" s="32" t="n"/>
-      <c r="U135" s="32" t="n"/>
-      <c r="V135" s="32" t="n"/>
-      <c r="W135" s="32" t="n"/>
-      <c r="X135" s="32" t="n"/>
-      <c r="Y135" s="32" t="n"/>
-      <c r="Z135" s="32" t="n"/>
-      <c r="AA135" s="33">
+      <c r="O135" s="36" t="n"/>
+      <c r="P135" s="36" t="n"/>
+      <c r="Q135" s="36" t="n"/>
+      <c r="R135" s="36" t="n"/>
+      <c r="S135" s="36" t="n"/>
+      <c r="T135" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" s="36" t="n"/>
+      <c r="V135" s="36" t="n"/>
+      <c r="W135" s="36" t="n"/>
+      <c r="X135" s="36" t="n"/>
+      <c r="Y135" s="36" t="n"/>
+      <c r="Z135" s="36" t="n"/>
+      <c r="AA135" s="37">
         <f>IF($G135="SUM",IF(COUNT($O135:$Z135)=0,"",SUM($O135:$Z135)),IF($G135="AVG",IFERROR(AVERAGE($O135:$Z135),""),IF($G135="LAST",IFERROR(LOOKUP(2,1/($O135:$Z135&lt;&gt;""),$O135:$Z135),""),"")))</f>
         <v/>
       </c>
@@ -13649,22 +13619,22 @@
       </c>
       <c r="B136" s="21" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>التدريب والتطوير</t>
+          <t>الحملات التسويقية</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>متوسط ساعات التدريب لكل موظف</t>
+          <t>حملات تسويقية منجزة</t>
         </is>
       </c>
       <c r="E136" s="25" t="inlineStr">
         <is>
-          <t>ساعة</t>
+          <t>حملة</t>
         </is>
       </c>
       <c r="F136" s="25" t="inlineStr">
@@ -13683,44 +13653,46 @@
         </is>
       </c>
       <c r="I136" s="27" t="n">
-        <v>0.05405</v>
-      </c>
-      <c r="J136" s="38" t="n">
-        <v>40</v>
+        <v>0.05556</v>
+      </c>
+      <c r="J136" s="28" t="n">
+        <v>48</v>
       </c>
       <c r="K136" s="29" t="inlineStr">
         <is>
-          <t>≥ 40 ساعة</t>
+          <t>48 حملة</t>
         </is>
       </c>
       <c r="L136" s="30" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>النمو</t>
         </is>
       </c>
       <c r="M136" s="31" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>زيادة وصول العملاء</t>
         </is>
       </c>
       <c r="N136" s="26" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
-        </is>
-      </c>
-      <c r="O136" s="39" t="n"/>
-      <c r="P136" s="39" t="n"/>
-      <c r="Q136" s="39" t="n"/>
-      <c r="R136" s="39" t="n"/>
-      <c r="S136" s="39" t="n"/>
-      <c r="T136" s="39" t="n"/>
-      <c r="U136" s="39" t="n"/>
-      <c r="V136" s="39" t="n"/>
-      <c r="W136" s="39" t="n"/>
-      <c r="X136" s="39" t="n"/>
-      <c r="Y136" s="39" t="n"/>
-      <c r="Z136" s="39" t="n"/>
-      <c r="AA136" s="40">
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="O136" s="32" t="n"/>
+      <c r="P136" s="32" t="n"/>
+      <c r="Q136" s="32" t="n"/>
+      <c r="R136" s="32" t="n"/>
+      <c r="S136" s="32" t="n"/>
+      <c r="T136" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="U136" s="32" t="n"/>
+      <c r="V136" s="32" t="n"/>
+      <c r="W136" s="32" t="n"/>
+      <c r="X136" s="32" t="n"/>
+      <c r="Y136" s="32" t="n"/>
+      <c r="Z136" s="32" t="n"/>
+      <c r="AA136" s="33">
         <f>IF($G136="SUM",IF(COUNT($O136:$Z136)=0,"",SUM($O136:$Z136)),IF($G136="AVG",IFERROR(AVERAGE($O136:$Z136),""),IF($G136="LAST",IFERROR(LOOKUP(2,1/($O136:$Z136&lt;&gt;""),$O136:$Z136),""),"")))</f>
         <v/>
       </c>
@@ -13739,17 +13711,17 @@
       </c>
       <c r="B137" s="21" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>التدريب والتطوير</t>
+          <t>الحملات التسويقية</t>
         </is>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>نسبة الموظفين المشمولين بخطة تطوير</t>
+          <t>تحويل الفرص إلى عقود</t>
         </is>
       </c>
       <c r="E137" s="25" t="inlineStr">
@@ -13764,38 +13736,38 @@
       </c>
       <c r="G137" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="H137" s="26" t="inlineStr">
         <is>
-          <t>🟠 مهم</t>
+          <t>🔴 رئيسي</t>
         </is>
       </c>
       <c r="I137" s="27" t="n">
-        <v>0.05405</v>
+        <v>0.08333</v>
       </c>
       <c r="J137" s="27" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="K137" s="29" t="inlineStr">
         <is>
-          <t>≥ 80%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L137" s="30" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>النمو</t>
         </is>
       </c>
       <c r="M137" s="31" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>زيادة وصول العملاء</t>
         </is>
       </c>
       <c r="N137" s="26" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="O137" s="36" t="n"/>
@@ -13803,7 +13775,9 @@
       <c r="Q137" s="36" t="n"/>
       <c r="R137" s="36" t="n"/>
       <c r="S137" s="36" t="n"/>
-      <c r="T137" s="36" t="n"/>
+      <c r="T137" s="36" t="n">
+        <v>0.17</v>
+      </c>
       <c r="U137" s="36" t="n"/>
       <c r="V137" s="36" t="n"/>
       <c r="W137" s="36" t="n"/>
@@ -13829,22 +13803,22 @@
       </c>
       <c r="B138" s="21" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>الرضا والثقافة</t>
+          <t>الحملات التسويقية</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>مؤشر رضا الموظفين (eNPS)</t>
+          <t>نسبة المبيعات لكل حملة</t>
         </is>
       </c>
       <c r="E138" s="25" t="inlineStr">
         <is>
-          <t>نقطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F138" s="25" t="inlineStr">
@@ -13863,44 +13837,46 @@
         </is>
       </c>
       <c r="I138" s="27" t="n">
-        <v>0.08108</v>
-      </c>
-      <c r="J138" s="38" t="n">
-        <v>30</v>
+        <v>0.08333</v>
+      </c>
+      <c r="J138" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="K138" s="29" t="inlineStr">
         <is>
-          <t>≥ 30</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="L138" s="30" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>النمو</t>
         </is>
       </c>
       <c r="M138" s="31" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>زيادة وصول العملاء</t>
         </is>
       </c>
       <c r="N138" s="26" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
-        </is>
-      </c>
-      <c r="O138" s="39" t="n"/>
-      <c r="P138" s="39" t="n"/>
-      <c r="Q138" s="39" t="n"/>
-      <c r="R138" s="39" t="n"/>
-      <c r="S138" s="39" t="n"/>
-      <c r="T138" s="39" t="n"/>
-      <c r="U138" s="39" t="n"/>
-      <c r="V138" s="39" t="n"/>
-      <c r="W138" s="39" t="n"/>
-      <c r="X138" s="39" t="n"/>
-      <c r="Y138" s="39" t="n"/>
-      <c r="Z138" s="39" t="n"/>
-      <c r="AA138" s="40">
+          <t>مالي</t>
+        </is>
+      </c>
+      <c r="O138" s="36" t="n"/>
+      <c r="P138" s="36" t="n"/>
+      <c r="Q138" s="36" t="n"/>
+      <c r="R138" s="36" t="n"/>
+      <c r="S138" s="36" t="n"/>
+      <c r="T138" s="36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U138" s="36" t="n"/>
+      <c r="V138" s="36" t="n"/>
+      <c r="W138" s="36" t="n"/>
+      <c r="X138" s="36" t="n"/>
+      <c r="Y138" s="36" t="n"/>
+      <c r="Z138" s="36" t="n"/>
+      <c r="AA138" s="37">
         <f>IF($G138="SUM",IF(COUNT($O138:$Z138)=0,"",SUM($O138:$Z138)),IF($G138="AVG",IFERROR(AVERAGE($O138:$Z138),""),IF($G138="LAST",IFERROR(LOOKUP(2,1/($O138:$Z138&lt;&gt;""),$O138:$Z138),""),"")))</f>
         <v/>
       </c>
@@ -13919,17 +13895,17 @@
       </c>
       <c r="B139" s="21" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>الرضا والثقافة</t>
+          <t>الدعاية والإعلان</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>تحسين مستوى الرضا الوظيفي</t>
+          <t>نسبة التزام الهوية البصرية</t>
         </is>
       </c>
       <c r="E139" s="25" t="inlineStr">
@@ -13944,7 +13920,7 @@
       </c>
       <c r="G139" s="25" t="inlineStr">
         <is>
-          <t>AVG</t>
+          <t>LAST</t>
         </is>
       </c>
       <c r="H139" s="26" t="inlineStr">
@@ -13953,27 +13929,29 @@
         </is>
       </c>
       <c r="I139" s="27" t="n">
-        <v>0.08108</v>
-      </c>
-      <c r="J139" s="25" t="inlineStr"/>
+        <v>0.08333</v>
+      </c>
+      <c r="J139" s="27" t="n">
+        <v>1</v>
+      </c>
       <c r="K139" s="29" t="inlineStr">
         <is>
-          <t>مستهدف سنوي</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="L139" s="30" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>الابتكار</t>
         </is>
       </c>
       <c r="M139" s="31" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>تطوير التصاميم والهوية</t>
         </is>
       </c>
       <c r="N139" s="26" t="inlineStr">
         <is>
-          <t>العملاء</t>
+          <t>التعلّم والنمو</t>
         </is>
       </c>
       <c r="O139" s="36" t="n"/>
@@ -13981,7 +13959,9 @@
       <c r="Q139" s="36" t="n"/>
       <c r="R139" s="36" t="n"/>
       <c r="S139" s="36" t="n"/>
-      <c r="T139" s="36" t="n"/>
+      <c r="T139" s="36" t="n">
+        <v>0.1</v>
+      </c>
       <c r="U139" s="36" t="n"/>
       <c r="V139" s="36" t="n"/>
       <c r="W139" s="36" t="n"/>
@@ -14007,22 +13987,22 @@
       </c>
       <c r="B140" s="21" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>الرضا والثقافة</t>
+          <t>العلاقات والشراكات</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>ترسيخ القيم والثقافة المؤسسية</t>
+          <t>وصول العلاقات العامة (PR)</t>
         </is>
       </c>
       <c r="E140" s="25" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>وصول</t>
         </is>
       </c>
       <c r="F140" s="25" t="inlineStr">
@@ -14041,44 +14021,46 @@
         </is>
       </c>
       <c r="I140" s="27" t="n">
-        <v>0.05405</v>
-      </c>
-      <c r="J140" s="27" t="n">
-        <v>1</v>
+        <v>0.05556</v>
+      </c>
+      <c r="J140" s="28" t="n">
+        <v>7000000</v>
       </c>
       <c r="K140" s="29" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7م وصول</t>
         </is>
       </c>
       <c r="L140" s="30" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>النمو</t>
         </is>
       </c>
       <c r="M140" s="31" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>زيادة وصول العملاء</t>
         </is>
       </c>
       <c r="N140" s="26" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O140" s="36" t="n"/>
-      <c r="P140" s="36" t="n"/>
-      <c r="Q140" s="36" t="n"/>
-      <c r="R140" s="36" t="n"/>
-      <c r="S140" s="36" t="n"/>
-      <c r="T140" s="36" t="n"/>
-      <c r="U140" s="36" t="n"/>
-      <c r="V140" s="36" t="n"/>
-      <c r="W140" s="36" t="n"/>
-      <c r="X140" s="36" t="n"/>
-      <c r="Y140" s="36" t="n"/>
-      <c r="Z140" s="36" t="n"/>
-      <c r="AA140" s="37">
+          <t>العملاء</t>
+        </is>
+      </c>
+      <c r="O140" s="32" t="n"/>
+      <c r="P140" s="32" t="n"/>
+      <c r="Q140" s="32" t="n"/>
+      <c r="R140" s="32" t="n"/>
+      <c r="S140" s="32" t="n"/>
+      <c r="T140" s="32" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="U140" s="32" t="n"/>
+      <c r="V140" s="32" t="n"/>
+      <c r="W140" s="32" t="n"/>
+      <c r="X140" s="32" t="n"/>
+      <c r="Y140" s="32" t="n"/>
+      <c r="Z140" s="32" t="n"/>
+      <c r="AA140" s="33">
         <f>IF($G140="SUM",IF(COUNT($O140:$Z140)=0,"",SUM($O140:$Z140)),IF($G140="AVG",IFERROR(AVERAGE($O140:$Z140),""),IF($G140="LAST",IFERROR(LOOKUP(2,1/($O140:$Z140&lt;&gt;""),$O140:$Z140),""),"")))</f>
         <v/>
       </c>
@@ -14097,22 +14079,22 @@
       </c>
       <c r="B141" s="21" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>الأتمتة والتوثيق</t>
+          <t>العلاقات والشراكات</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>نسبة أتمتة عمليات الموارد البشرية</t>
+          <t>عدد المعارض بالسنة</t>
         </is>
       </c>
       <c r="E141" s="25" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>معرض</t>
         </is>
       </c>
       <c r="F141" s="25" t="inlineStr">
@@ -14122,7 +14104,7 @@
       </c>
       <c r="G141" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="H141" s="26" t="inlineStr">
@@ -14131,14 +14113,14 @@
         </is>
       </c>
       <c r="I141" s="27" t="n">
-        <v>0.05405</v>
-      </c>
-      <c r="J141" s="27" t="n">
-        <v>1</v>
+        <v>0.05556</v>
+      </c>
+      <c r="J141" s="28" t="n">
+        <v>3</v>
       </c>
       <c r="K141" s="29" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3 معارض</t>
         </is>
       </c>
       <c r="L141" s="30" t="inlineStr">
@@ -14148,27 +14130,29 @@
       </c>
       <c r="M141" s="31" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>إطلاق مشاريع جديدة</t>
         </is>
       </c>
       <c r="N141" s="26" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
-        </is>
-      </c>
-      <c r="O141" s="36" t="n"/>
-      <c r="P141" s="36" t="n"/>
-      <c r="Q141" s="36" t="n"/>
-      <c r="R141" s="36" t="n"/>
-      <c r="S141" s="36" t="n"/>
-      <c r="T141" s="36" t="n"/>
-      <c r="U141" s="36" t="n"/>
-      <c r="V141" s="36" t="n"/>
-      <c r="W141" s="36" t="n"/>
-      <c r="X141" s="36" t="n"/>
-      <c r="Y141" s="36" t="n"/>
-      <c r="Z141" s="36" t="n"/>
-      <c r="AA141" s="37">
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="O141" s="32" t="n"/>
+      <c r="P141" s="32" t="n"/>
+      <c r="Q141" s="32" t="n"/>
+      <c r="R141" s="32" t="n"/>
+      <c r="S141" s="32" t="n"/>
+      <c r="T141" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" s="32" t="n"/>
+      <c r="V141" s="32" t="n"/>
+      <c r="W141" s="32" t="n"/>
+      <c r="X141" s="32" t="n"/>
+      <c r="Y141" s="32" t="n"/>
+      <c r="Z141" s="32" t="n"/>
+      <c r="AA141" s="33">
         <f>IF($G141="SUM",IF(COUNT($O141:$Z141)=0,"",SUM($O141:$Z141)),IF($G141="AVG",IFERROR(AVERAGE($O141:$Z141),""),IF($G141="LAST",IFERROR(LOOKUP(2,1/($O141:$Z141&lt;&gt;""),$O141:$Z141),""),"")))</f>
         <v/>
       </c>
@@ -14187,22 +14171,22 @@
       </c>
       <c r="B142" s="21" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>الأتمتة والتوثيق</t>
+          <t>العلاقات والشراكات</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>نسبة توثيق أنظمة العمل</t>
+          <t>اتفاقيات استراتيجية</t>
         </is>
       </c>
       <c r="E142" s="25" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>اتفاقية</t>
         </is>
       </c>
       <c r="F142" s="25" t="inlineStr">
@@ -14212,33 +14196,33 @@
       </c>
       <c r="G142" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="H142" s="26" t="inlineStr">
         <is>
-          <t>🟡 متابعة</t>
+          <t>🟠 مهم</t>
         </is>
       </c>
       <c r="I142" s="27" t="n">
-        <v>0.02703</v>
-      </c>
-      <c r="J142" s="27" t="n">
-        <v>0.8</v>
+        <v>0.05556</v>
+      </c>
+      <c r="J142" s="28" t="n">
+        <v>3</v>
       </c>
       <c r="K142" s="29" t="inlineStr">
         <is>
-          <t>≥ 80%</t>
+          <t>3 اتفاقيات</t>
         </is>
       </c>
       <c r="L142" s="30" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>الابتكار</t>
         </is>
       </c>
       <c r="M142" s="31" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>إطلاق مشاريع جديدة</t>
         </is>
       </c>
       <c r="N142" s="26" t="inlineStr">
@@ -14246,19 +14230,21 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="O142" s="36" t="n"/>
-      <c r="P142" s="36" t="n"/>
-      <c r="Q142" s="36" t="n"/>
-      <c r="R142" s="36" t="n"/>
-      <c r="S142" s="36" t="n"/>
-      <c r="T142" s="36" t="n"/>
-      <c r="U142" s="36" t="n"/>
-      <c r="V142" s="36" t="n"/>
-      <c r="W142" s="36" t="n"/>
-      <c r="X142" s="36" t="n"/>
-      <c r="Y142" s="36" t="n"/>
-      <c r="Z142" s="36" t="n"/>
-      <c r="AA142" s="37">
+      <c r="O142" s="32" t="n"/>
+      <c r="P142" s="32" t="n"/>
+      <c r="Q142" s="32" t="n"/>
+      <c r="R142" s="32" t="n"/>
+      <c r="S142" s="32" t="n"/>
+      <c r="T142" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" s="32" t="n"/>
+      <c r="V142" s="32" t="n"/>
+      <c r="W142" s="32" t="n"/>
+      <c r="X142" s="32" t="n"/>
+      <c r="Y142" s="32" t="n"/>
+      <c r="Z142" s="32" t="n"/>
+      <c r="AA142" s="33">
         <f>IF($G142="SUM",IF(COUNT($O142:$Z142)=0,"",SUM($O142:$Z142)),IF($G142="AVG",IFERROR(AVERAGE($O142:$Z142),""),IF($G142="LAST",IFERROR(LOOKUP(2,1/($O142:$Z142&lt;&gt;""),$O142:$Z142),""),"")))</f>
         <v/>
       </c>
@@ -14277,22 +14263,22 @@
       </c>
       <c r="B143" s="21" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>الأتمتة والتوثيق</t>
+          <t>خدمة العملاء والدعم</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>ترسيخ الأنظمة الإدارية</t>
+          <t>تقييم خرائط قوقل</t>
         </is>
       </c>
       <c r="E143" s="25" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>نجمة/5</t>
         </is>
       </c>
       <c r="F143" s="25" t="inlineStr">
@@ -14302,7 +14288,7 @@
       </c>
       <c r="G143" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="H143" s="26" t="inlineStr">
@@ -14311,14 +14297,14 @@
         </is>
       </c>
       <c r="I143" s="27" t="n">
-        <v>0.05405</v>
-      </c>
-      <c r="J143" s="27" t="n">
-        <v>0.8</v>
+        <v>0.05556</v>
+      </c>
+      <c r="J143" s="38" t="n">
+        <v>4.7</v>
       </c>
       <c r="K143" s="29" t="inlineStr">
         <is>
-          <t>≥ 80%</t>
+          <t>4.7 ⭐</t>
         </is>
       </c>
       <c r="L143" s="30" t="inlineStr">
@@ -14328,27 +14314,29 @@
       </c>
       <c r="M143" s="31" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>تعزيز تجربة العملاء</t>
         </is>
       </c>
       <c r="N143" s="26" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O143" s="36" t="n"/>
-      <c r="P143" s="36" t="n"/>
-      <c r="Q143" s="36" t="n"/>
-      <c r="R143" s="36" t="n"/>
-      <c r="S143" s="36" t="n"/>
-      <c r="T143" s="36" t="n"/>
-      <c r="U143" s="36" t="n"/>
-      <c r="V143" s="36" t="n"/>
-      <c r="W143" s="36" t="n"/>
-      <c r="X143" s="36" t="n"/>
-      <c r="Y143" s="36" t="n"/>
-      <c r="Z143" s="36" t="n"/>
-      <c r="AA143" s="37">
+          <t>العملاء</t>
+        </is>
+      </c>
+      <c r="O143" s="39" t="n"/>
+      <c r="P143" s="39" t="n"/>
+      <c r="Q143" s="39" t="n"/>
+      <c r="R143" s="39" t="n"/>
+      <c r="S143" s="39" t="n"/>
+      <c r="T143" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U143" s="39" t="n"/>
+      <c r="V143" s="39" t="n"/>
+      <c r="W143" s="39" t="n"/>
+      <c r="X143" s="39" t="n"/>
+      <c r="Y143" s="39" t="n"/>
+      <c r="Z143" s="39" t="n"/>
+      <c r="AA143" s="40">
         <f>IF($G143="SUM",IF(COUNT($O143:$Z143)=0,"",SUM($O143:$Z143)),IF($G143="AVG",IFERROR(AVERAGE($O143:$Z143),""),IF($G143="LAST",IFERROR(LOOKUP(2,1/($O143:$Z143&lt;&gt;""),$O143:$Z143),""),"")))</f>
         <v/>
       </c>
@@ -14367,17 +14355,17 @@
       </c>
       <c r="B144" s="21" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C144" s="9" t="inlineStr">
         <is>
-          <t>الهيكلة</t>
+          <t>خدمة العملاء والدعم</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>اعتماد الهيكل التنظيمي</t>
+          <t>معدل خفض الشكاوى</t>
         </is>
       </c>
       <c r="E144" s="25" t="inlineStr">
@@ -14392,7 +14380,7 @@
       </c>
       <c r="G144" s="25" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="H144" s="26" t="inlineStr">
@@ -14401,14 +14389,14 @@
         </is>
       </c>
       <c r="I144" s="27" t="n">
-        <v>0.05405</v>
+        <v>0.05556</v>
       </c>
       <c r="J144" s="27" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="K144" s="29" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="L144" s="30" t="inlineStr">
@@ -14418,12 +14406,12 @@
       </c>
       <c r="M144" s="31" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>تعزيز تجربة العملاء</t>
         </is>
       </c>
       <c r="N144" s="26" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>العملاء</t>
         </is>
       </c>
       <c r="O144" s="36" t="n"/>
@@ -14431,7 +14419,9 @@
       <c r="Q144" s="36" t="n"/>
       <c r="R144" s="36" t="n"/>
       <c r="S144" s="36" t="n"/>
-      <c r="T144" s="36" t="n"/>
+      <c r="T144" s="36" t="n">
+        <v>0.21</v>
+      </c>
       <c r="U144" s="36" t="n"/>
       <c r="V144" s="36" t="n"/>
       <c r="W144" s="36" t="n"/>
@@ -14457,22 +14447,22 @@
       </c>
       <c r="B145" s="21" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>الهيكلة</t>
+          <t>تطبيق تانكي</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>اكتمال الأوصاف الوظيفية (+KPI)</t>
+          <t>وصول محتوى تطبيق تانكي</t>
         </is>
       </c>
       <c r="E145" s="25" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>وصول</t>
         </is>
       </c>
       <c r="F145" s="25" t="inlineStr">
@@ -14491,44 +14481,44 @@
         </is>
       </c>
       <c r="I145" s="27" t="n">
-        <v>0.05405</v>
-      </c>
-      <c r="J145" s="27" t="n">
-        <v>1</v>
+        <v>0.05556</v>
+      </c>
+      <c r="J145" s="28" t="n">
+        <v>1000000</v>
       </c>
       <c r="K145" s="29" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1م وصول</t>
         </is>
       </c>
       <c r="L145" s="30" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>الابتكار</t>
         </is>
       </c>
       <c r="M145" s="31" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>تطبيق «تانكي»</t>
         </is>
       </c>
       <c r="N145" s="26" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O145" s="36" t="n"/>
-      <c r="P145" s="36" t="n"/>
-      <c r="Q145" s="36" t="n"/>
-      <c r="R145" s="36" t="n"/>
-      <c r="S145" s="36" t="n"/>
-      <c r="T145" s="36" t="n"/>
-      <c r="U145" s="36" t="n"/>
-      <c r="V145" s="36" t="n"/>
-      <c r="W145" s="36" t="n"/>
-      <c r="X145" s="36" t="n"/>
-      <c r="Y145" s="36" t="n"/>
-      <c r="Z145" s="36" t="n"/>
-      <c r="AA145" s="37">
+          <t>العملاء</t>
+        </is>
+      </c>
+      <c r="O145" s="32" t="n"/>
+      <c r="P145" s="32" t="n"/>
+      <c r="Q145" s="32" t="n"/>
+      <c r="R145" s="32" t="n"/>
+      <c r="S145" s="32" t="n"/>
+      <c r="T145" s="32" t="n"/>
+      <c r="U145" s="32" t="n"/>
+      <c r="V145" s="32" t="n"/>
+      <c r="W145" s="32" t="n"/>
+      <c r="X145" s="32" t="n"/>
+      <c r="Y145" s="32" t="n"/>
+      <c r="Z145" s="32" t="n"/>
+      <c r="AA145" s="33">
         <f>IF($G145="SUM",IF(COUNT($O145:$Z145)=0,"",SUM($O145:$Z145)),IF($G145="AVG",IFERROR(AVERAGE($O145:$Z145),""),IF($G145="LAST",IFERROR(LOOKUP(2,1/($O145:$Z145&lt;&gt;""),$O145:$Z145),""),"")))</f>
         <v/>
       </c>
@@ -14547,22 +14537,22 @@
       </c>
       <c r="B146" s="21" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>الأداء</t>
+          <t>تطبيق تانكي</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>نسبة إنجاز تقييمات الأداء في موعدها</t>
+          <t>مشاركات تطبيق تانكي</t>
         </is>
       </c>
       <c r="E146" s="25" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مشاركة</t>
         </is>
       </c>
       <c r="F146" s="25" t="inlineStr">
@@ -14572,7 +14562,7 @@
       </c>
       <c r="G146" s="25" t="inlineStr">
         <is>
-          <t>AVG</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="H146" s="26" t="inlineStr">
@@ -14581,24 +14571,24 @@
         </is>
       </c>
       <c r="I146" s="27" t="n">
-        <v>0.05405</v>
-      </c>
-      <c r="J146" s="27" t="n">
-        <v>1</v>
+        <v>0.05556</v>
+      </c>
+      <c r="J146" s="28" t="n">
+        <v>250</v>
       </c>
       <c r="K146" s="29" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>250 مشاركة</t>
         </is>
       </c>
       <c r="L146" s="30" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>الابتكار</t>
         </is>
       </c>
       <c r="M146" s="31" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>تطبيق «تانكي»</t>
         </is>
       </c>
       <c r="N146" s="26" t="inlineStr">
@@ -14606,19 +14596,19 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="O146" s="36" t="n"/>
-      <c r="P146" s="36" t="n"/>
-      <c r="Q146" s="36" t="n"/>
-      <c r="R146" s="36" t="n"/>
-      <c r="S146" s="36" t="n"/>
-      <c r="T146" s="36" t="n"/>
-      <c r="U146" s="36" t="n"/>
-      <c r="V146" s="36" t="n"/>
-      <c r="W146" s="36" t="n"/>
-      <c r="X146" s="36" t="n"/>
-      <c r="Y146" s="36" t="n"/>
-      <c r="Z146" s="36" t="n"/>
-      <c r="AA146" s="37">
+      <c r="O146" s="32" t="n"/>
+      <c r="P146" s="32" t="n"/>
+      <c r="Q146" s="32" t="n"/>
+      <c r="R146" s="32" t="n"/>
+      <c r="S146" s="32" t="n"/>
+      <c r="T146" s="32" t="n"/>
+      <c r="U146" s="32" t="n"/>
+      <c r="V146" s="32" t="n"/>
+      <c r="W146" s="32" t="n"/>
+      <c r="X146" s="32" t="n"/>
+      <c r="Y146" s="32" t="n"/>
+      <c r="Z146" s="32" t="n"/>
+      <c r="AA146" s="33">
         <f>IF($G146="SUM",IF(COUNT($O146:$Z146)=0,"",SUM($O146:$Z146)),IF($G146="AVG",IFERROR(AVERAGE($O146:$Z146),""),IF($G146="LAST",IFERROR(LOOKUP(2,1/($O146:$Z146&lt;&gt;""),$O146:$Z146),""),"")))</f>
         <v/>
       </c>
@@ -14631,1390 +14621,14 @@
         <v/>
       </c>
     </row>
-    <row r="147" ht="24" customHeight="1">
-      <c r="A147" s="15" t="n">
-        <v>144</v>
-      </c>
-      <c r="B147" s="21" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C147" s="9" t="inlineStr">
-        <is>
-          <t>الإدارة العامة</t>
-        </is>
-      </c>
-      <c r="D147" s="9" t="inlineStr">
-        <is>
-          <t>الوصول الكلي (Total Reach)</t>
-        </is>
-      </c>
-      <c r="E147" s="25" t="inlineStr">
-        <is>
-          <t>وصول</t>
-        </is>
-      </c>
-      <c r="F147" s="25" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G147" s="25" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="H147" s="26" t="inlineStr">
-        <is>
-          <t>🔴 رئيسي</t>
-        </is>
-      </c>
-      <c r="I147" s="27" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="J147" s="28" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="K147" s="29" t="inlineStr">
-        <is>
-          <t>50م وصول</t>
-        </is>
-      </c>
-      <c r="L147" s="30" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="M147" s="31" t="inlineStr">
-        <is>
-          <t>زيادة وصول العملاء</t>
-        </is>
-      </c>
-      <c r="N147" s="26" t="inlineStr">
-        <is>
-          <t>العملاء</t>
-        </is>
-      </c>
-      <c r="O147" s="32" t="n"/>
-      <c r="P147" s="32" t="n"/>
-      <c r="Q147" s="32" t="n"/>
-      <c r="R147" s="32" t="n"/>
-      <c r="S147" s="32" t="n"/>
-      <c r="T147" s="32" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="U147" s="32" t="n"/>
-      <c r="V147" s="32" t="n"/>
-      <c r="W147" s="32" t="n"/>
-      <c r="X147" s="32" t="n"/>
-      <c r="Y147" s="32" t="n"/>
-      <c r="Z147" s="32" t="n"/>
-      <c r="AA147" s="33">
-        <f>IF($G147="SUM",IF(COUNT($O147:$Z147)=0,"",SUM($O147:$Z147)),IF($G147="AVG",IFERROR(AVERAGE($O147:$Z147),""),IF($G147="LAST",IFERROR(LOOKUP(2,1/($O147:$Z147&lt;&gt;""),$O147:$Z147),""),"")))</f>
-        <v/>
-      </c>
-      <c r="AB147" s="16">
-        <f>IF($J147="","",IF($AA147="","",IF($J147=0,IF($AA147&lt;=0,1,0),IF($F147="↓",IFERROR($J147/$AA147,0),IFERROR($AA147/$J147,0)))))</f>
-        <v/>
-      </c>
-      <c r="AC147" s="15">
-        <f>IF($AB147="","—",IF($AB147&gt;=1,"✅ محقق",IF($AB147&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148" ht="24" customHeight="1">
-      <c r="A148" s="15" t="n">
-        <v>145</v>
-      </c>
-      <c r="B148" s="21" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C148" s="9" t="inlineStr">
-        <is>
-          <t>الإدارة العامة</t>
-        </is>
-      </c>
-      <c r="D148" s="9" t="inlineStr">
-        <is>
-          <t>عملاء تجاريون جدد</t>
-        </is>
-      </c>
-      <c r="E148" s="25" t="inlineStr">
-        <is>
-          <t>عميل</t>
-        </is>
-      </c>
-      <c r="F148" s="25" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G148" s="25" t="inlineStr">
-        <is>
-          <t>SUM</t>
-        </is>
-      </c>
-      <c r="H148" s="26" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="I148" s="27" t="n">
-        <v>0.05556</v>
-      </c>
-      <c r="J148" s="28" t="n">
-        <v>200</v>
-      </c>
-      <c r="K148" s="29" t="inlineStr">
-        <is>
-          <t>200 عميل</t>
-        </is>
-      </c>
-      <c r="L148" s="30" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="M148" s="31" t="inlineStr">
-        <is>
-          <t>زيادة وصول العملاء</t>
-        </is>
-      </c>
-      <c r="N148" s="26" t="inlineStr">
-        <is>
-          <t>العملاء</t>
-        </is>
-      </c>
-      <c r="O148" s="32" t="n"/>
-      <c r="P148" s="32" t="n"/>
-      <c r="Q148" s="32" t="n"/>
-      <c r="R148" s="32" t="n"/>
-      <c r="S148" s="32" t="n"/>
-      <c r="T148" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="U148" s="32" t="n"/>
-      <c r="V148" s="32" t="n"/>
-      <c r="W148" s="32" t="n"/>
-      <c r="X148" s="32" t="n"/>
-      <c r="Y148" s="32" t="n"/>
-      <c r="Z148" s="32" t="n"/>
-      <c r="AA148" s="33">
-        <f>IF($G148="SUM",IF(COUNT($O148:$Z148)=0,"",SUM($O148:$Z148)),IF($G148="AVG",IFERROR(AVERAGE($O148:$Z148),""),IF($G148="LAST",IFERROR(LOOKUP(2,1/($O148:$Z148&lt;&gt;""),$O148:$Z148),""),"")))</f>
-        <v/>
-      </c>
-      <c r="AB148" s="16">
-        <f>IF($J148="","",IF($AA148="","",IF($J148=0,IF($AA148&lt;=0,1,0),IF($F148="↓",IFERROR($J148/$AA148,0),IFERROR($AA148/$J148,0)))))</f>
-        <v/>
-      </c>
-      <c r="AC148" s="15">
-        <f>IF($AB148="","—",IF($AB148&gt;=1,"✅ محقق",IF($AB148&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149" ht="24" customHeight="1">
-      <c r="A149" s="15" t="n">
-        <v>146</v>
-      </c>
-      <c r="B149" s="21" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C149" s="9" t="inlineStr">
-        <is>
-          <t>الفريق الإبداعي</t>
-        </is>
-      </c>
-      <c r="D149" s="9" t="inlineStr">
-        <is>
-          <t>إجمالي المتابعين (كل المنصات)</t>
-        </is>
-      </c>
-      <c r="E149" s="25" t="inlineStr">
-        <is>
-          <t>متابع</t>
-        </is>
-      </c>
-      <c r="F149" s="25" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G149" s="25" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="H149" s="26" t="inlineStr">
-        <is>
-          <t>🔴 رئيسي</t>
-        </is>
-      </c>
-      <c r="I149" s="27" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="J149" s="28" t="n">
-        <v>380000</v>
-      </c>
-      <c r="K149" s="29" t="inlineStr">
-        <is>
-          <t>380ك متابع</t>
-        </is>
-      </c>
-      <c r="L149" s="30" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="M149" s="31" t="inlineStr">
-        <is>
-          <t>زيادة وصول العملاء</t>
-        </is>
-      </c>
-      <c r="N149" s="26" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O149" s="32" t="n"/>
-      <c r="P149" s="32" t="n"/>
-      <c r="Q149" s="32" t="n"/>
-      <c r="R149" s="32" t="n"/>
-      <c r="S149" s="32" t="n"/>
-      <c r="T149" s="32" t="n">
-        <v>253000</v>
-      </c>
-      <c r="U149" s="32" t="n"/>
-      <c r="V149" s="32" t="n"/>
-      <c r="W149" s="32" t="n"/>
-      <c r="X149" s="32" t="n"/>
-      <c r="Y149" s="32" t="n"/>
-      <c r="Z149" s="32" t="n"/>
-      <c r="AA149" s="33">
-        <f>IF($G149="SUM",IF(COUNT($O149:$Z149)=0,"",SUM($O149:$Z149)),IF($G149="AVG",IFERROR(AVERAGE($O149:$Z149),""),IF($G149="LAST",IFERROR(LOOKUP(2,1/($O149:$Z149&lt;&gt;""),$O149:$Z149),""),"")))</f>
-        <v/>
-      </c>
-      <c r="AB149" s="16">
-        <f>IF($J149="","",IF($AA149="","",IF($J149=0,IF($AA149&lt;=0,1,0),IF($F149="↓",IFERROR($J149/$AA149,0),IFERROR($AA149/$J149,0)))))</f>
-        <v/>
-      </c>
-      <c r="AC149" s="15">
-        <f>IF($AB149="","—",IF($AB149&gt;=1,"✅ محقق",IF($AB149&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150" ht="24" customHeight="1">
-      <c r="A150" s="15" t="n">
-        <v>147</v>
-      </c>
-      <c r="B150" s="21" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C150" s="9" t="inlineStr">
-        <is>
-          <t>الفريق الإبداعي</t>
-        </is>
-      </c>
-      <c r="D150" s="9" t="inlineStr">
-        <is>
-          <t>معدل التفاعل (Engagement)</t>
-        </is>
-      </c>
-      <c r="E150" s="25" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F150" s="25" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G150" s="25" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="H150" s="26" t="inlineStr">
-        <is>
-          <t>🔴 رئيسي</t>
-        </is>
-      </c>
-      <c r="I150" s="27" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="J150" s="27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K150" s="29" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L150" s="30" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="M150" s="31" t="inlineStr">
-        <is>
-          <t>زيادة وصول العملاء</t>
-        </is>
-      </c>
-      <c r="N150" s="26" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O150" s="36" t="n"/>
-      <c r="P150" s="36" t="n"/>
-      <c r="Q150" s="36" t="n"/>
-      <c r="R150" s="36" t="n"/>
-      <c r="S150" s="36" t="n"/>
-      <c r="T150" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" s="36" t="n"/>
-      <c r="V150" s="36" t="n"/>
-      <c r="W150" s="36" t="n"/>
-      <c r="X150" s="36" t="n"/>
-      <c r="Y150" s="36" t="n"/>
-      <c r="Z150" s="36" t="n"/>
-      <c r="AA150" s="37">
-        <f>IF($G150="SUM",IF(COUNT($O150:$Z150)=0,"",SUM($O150:$Z150)),IF($G150="AVG",IFERROR(AVERAGE($O150:$Z150),""),IF($G150="LAST",IFERROR(LOOKUP(2,1/($O150:$Z150&lt;&gt;""),$O150:$Z150),""),"")))</f>
-        <v/>
-      </c>
-      <c r="AB150" s="16">
-        <f>IF($J150="","",IF($AA150="","",IF($J150=0,IF($AA150&lt;=0,1,0),IF($F150="↓",IFERROR($J150/$AA150,0),IFERROR($AA150/$J150,0)))))</f>
-        <v/>
-      </c>
-      <c r="AC150" s="15">
-        <f>IF($AB150="","—",IF($AB150&gt;=1,"✅ محقق",IF($AB150&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151" ht="24" customHeight="1">
-      <c r="A151" s="15" t="n">
-        <v>148</v>
-      </c>
-      <c r="B151" s="21" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C151" s="9" t="inlineStr">
-        <is>
-          <t>الحملات التسويقية</t>
-        </is>
-      </c>
-      <c r="D151" s="9" t="inlineStr">
-        <is>
-          <t>حملات تسويقية منجزة</t>
-        </is>
-      </c>
-      <c r="E151" s="25" t="inlineStr">
-        <is>
-          <t>حملة</t>
-        </is>
-      </c>
-      <c r="F151" s="25" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G151" s="25" t="inlineStr">
-        <is>
-          <t>SUM</t>
-        </is>
-      </c>
-      <c r="H151" s="26" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="I151" s="27" t="n">
-        <v>0.05556</v>
-      </c>
-      <c r="J151" s="28" t="n">
-        <v>48</v>
-      </c>
-      <c r="K151" s="29" t="inlineStr">
-        <is>
-          <t>48 حملة</t>
-        </is>
-      </c>
-      <c r="L151" s="30" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="M151" s="31" t="inlineStr">
-        <is>
-          <t>زيادة وصول العملاء</t>
-        </is>
-      </c>
-      <c r="N151" s="26" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O151" s="32" t="n"/>
-      <c r="P151" s="32" t="n"/>
-      <c r="Q151" s="32" t="n"/>
-      <c r="R151" s="32" t="n"/>
-      <c r="S151" s="32" t="n"/>
-      <c r="T151" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="U151" s="32" t="n"/>
-      <c r="V151" s="32" t="n"/>
-      <c r="W151" s="32" t="n"/>
-      <c r="X151" s="32" t="n"/>
-      <c r="Y151" s="32" t="n"/>
-      <c r="Z151" s="32" t="n"/>
-      <c r="AA151" s="33">
-        <f>IF($G151="SUM",IF(COUNT($O151:$Z151)=0,"",SUM($O151:$Z151)),IF($G151="AVG",IFERROR(AVERAGE($O151:$Z151),""),IF($G151="LAST",IFERROR(LOOKUP(2,1/($O151:$Z151&lt;&gt;""),$O151:$Z151),""),"")))</f>
-        <v/>
-      </c>
-      <c r="AB151" s="16">
-        <f>IF($J151="","",IF($AA151="","",IF($J151=0,IF($AA151&lt;=0,1,0),IF($F151="↓",IFERROR($J151/$AA151,0),IFERROR($AA151/$J151,0)))))</f>
-        <v/>
-      </c>
-      <c r="AC151" s="15">
-        <f>IF($AB151="","—",IF($AB151&gt;=1,"✅ محقق",IF($AB151&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152" ht="24" customHeight="1">
-      <c r="A152" s="15" t="n">
-        <v>149</v>
-      </c>
-      <c r="B152" s="21" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C152" s="9" t="inlineStr">
-        <is>
-          <t>الحملات التسويقية</t>
-        </is>
-      </c>
-      <c r="D152" s="9" t="inlineStr">
-        <is>
-          <t>تحويل الفرص إلى عقود</t>
-        </is>
-      </c>
-      <c r="E152" s="25" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F152" s="25" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G152" s="25" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="H152" s="26" t="inlineStr">
-        <is>
-          <t>🔴 رئيسي</t>
-        </is>
-      </c>
-      <c r="I152" s="27" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="J152" s="27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K152" s="29" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L152" s="30" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="M152" s="31" t="inlineStr">
-        <is>
-          <t>زيادة وصول العملاء</t>
-        </is>
-      </c>
-      <c r="N152" s="26" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O152" s="36" t="n"/>
-      <c r="P152" s="36" t="n"/>
-      <c r="Q152" s="36" t="n"/>
-      <c r="R152" s="36" t="n"/>
-      <c r="S152" s="36" t="n"/>
-      <c r="T152" s="36" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="U152" s="36" t="n"/>
-      <c r="V152" s="36" t="n"/>
-      <c r="W152" s="36" t="n"/>
-      <c r="X152" s="36" t="n"/>
-      <c r="Y152" s="36" t="n"/>
-      <c r="Z152" s="36" t="n"/>
-      <c r="AA152" s="37">
-        <f>IF($G152="SUM",IF(COUNT($O152:$Z152)=0,"",SUM($O152:$Z152)),IF($G152="AVG",IFERROR(AVERAGE($O152:$Z152),""),IF($G152="LAST",IFERROR(LOOKUP(2,1/($O152:$Z152&lt;&gt;""),$O152:$Z152),""),"")))</f>
-        <v/>
-      </c>
-      <c r="AB152" s="16">
-        <f>IF($J152="","",IF($AA152="","",IF($J152=0,IF($AA152&lt;=0,1,0),IF($F152="↓",IFERROR($J152/$AA152,0),IFERROR($AA152/$J152,0)))))</f>
-        <v/>
-      </c>
-      <c r="AC152" s="15">
-        <f>IF($AB152="","—",IF($AB152&gt;=1,"✅ محقق",IF($AB152&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153" ht="24" customHeight="1">
-      <c r="A153" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="B153" s="21" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C153" s="9" t="inlineStr">
-        <is>
-          <t>الحملات التسويقية</t>
-        </is>
-      </c>
-      <c r="D153" s="9" t="inlineStr">
-        <is>
-          <t>نسبة المبيعات لكل حملة</t>
-        </is>
-      </c>
-      <c r="E153" s="25" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F153" s="25" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G153" s="25" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="H153" s="26" t="inlineStr">
-        <is>
-          <t>🔴 رئيسي</t>
-        </is>
-      </c>
-      <c r="I153" s="27" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="J153" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K153" s="29" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L153" s="30" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="M153" s="31" t="inlineStr">
-        <is>
-          <t>زيادة وصول العملاء</t>
-        </is>
-      </c>
-      <c r="N153" s="26" t="inlineStr">
-        <is>
-          <t>مالي</t>
-        </is>
-      </c>
-      <c r="O153" s="36" t="n"/>
-      <c r="P153" s="36" t="n"/>
-      <c r="Q153" s="36" t="n"/>
-      <c r="R153" s="36" t="n"/>
-      <c r="S153" s="36" t="n"/>
-      <c r="T153" s="36" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U153" s="36" t="n"/>
-      <c r="V153" s="36" t="n"/>
-      <c r="W153" s="36" t="n"/>
-      <c r="X153" s="36" t="n"/>
-      <c r="Y153" s="36" t="n"/>
-      <c r="Z153" s="36" t="n"/>
-      <c r="AA153" s="37">
-        <f>IF($G153="SUM",IF(COUNT($O153:$Z153)=0,"",SUM($O153:$Z153)),IF($G153="AVG",IFERROR(AVERAGE($O153:$Z153),""),IF($G153="LAST",IFERROR(LOOKUP(2,1/($O153:$Z153&lt;&gt;""),$O153:$Z153),""),"")))</f>
-        <v/>
-      </c>
-      <c r="AB153" s="16">
-        <f>IF($J153="","",IF($AA153="","",IF($J153=0,IF($AA153&lt;=0,1,0),IF($F153="↓",IFERROR($J153/$AA153,0),IFERROR($AA153/$J153,0)))))</f>
-        <v/>
-      </c>
-      <c r="AC153" s="15">
-        <f>IF($AB153="","—",IF($AB153&gt;=1,"✅ محقق",IF($AB153&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154" ht="24" customHeight="1">
-      <c r="A154" s="15" t="n">
-        <v>151</v>
-      </c>
-      <c r="B154" s="21" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C154" s="9" t="inlineStr">
-        <is>
-          <t>الدعاية والإعلان</t>
-        </is>
-      </c>
-      <c r="D154" s="9" t="inlineStr">
-        <is>
-          <t>نسبة التزام الهوية البصرية</t>
-        </is>
-      </c>
-      <c r="E154" s="25" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F154" s="25" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G154" s="25" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="H154" s="26" t="inlineStr">
-        <is>
-          <t>🔴 رئيسي</t>
-        </is>
-      </c>
-      <c r="I154" s="27" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="J154" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K154" s="29" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L154" s="30" t="inlineStr">
-        <is>
-          <t>الابتكار</t>
-        </is>
-      </c>
-      <c r="M154" s="31" t="inlineStr">
-        <is>
-          <t>تطوير التصاميم والهوية</t>
-        </is>
-      </c>
-      <c r="N154" s="26" t="inlineStr">
-        <is>
-          <t>التعلّم والنمو</t>
-        </is>
-      </c>
-      <c r="O154" s="36" t="n"/>
-      <c r="P154" s="36" t="n"/>
-      <c r="Q154" s="36" t="n"/>
-      <c r="R154" s="36" t="n"/>
-      <c r="S154" s="36" t="n"/>
-      <c r="T154" s="36" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U154" s="36" t="n"/>
-      <c r="V154" s="36" t="n"/>
-      <c r="W154" s="36" t="n"/>
-      <c r="X154" s="36" t="n"/>
-      <c r="Y154" s="36" t="n"/>
-      <c r="Z154" s="36" t="n"/>
-      <c r="AA154" s="37">
-        <f>IF($G154="SUM",IF(COUNT($O154:$Z154)=0,"",SUM($O154:$Z154)),IF($G154="AVG",IFERROR(AVERAGE($O154:$Z154),""),IF($G154="LAST",IFERROR(LOOKUP(2,1/($O154:$Z154&lt;&gt;""),$O154:$Z154),""),"")))</f>
-        <v/>
-      </c>
-      <c r="AB154" s="16">
-        <f>IF($J154="","",IF($AA154="","",IF($J154=0,IF($AA154&lt;=0,1,0),IF($F154="↓",IFERROR($J154/$AA154,0),IFERROR($AA154/$J154,0)))))</f>
-        <v/>
-      </c>
-      <c r="AC154" s="15">
-        <f>IF($AB154="","—",IF($AB154&gt;=1,"✅ محقق",IF($AB154&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155" ht="24" customHeight="1">
-      <c r="A155" s="15" t="n">
-        <v>152</v>
-      </c>
-      <c r="B155" s="21" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C155" s="9" t="inlineStr">
-        <is>
-          <t>العلاقات والشراكات</t>
-        </is>
-      </c>
-      <c r="D155" s="9" t="inlineStr">
-        <is>
-          <t>وصول العلاقات العامة (PR)</t>
-        </is>
-      </c>
-      <c r="E155" s="25" t="inlineStr">
-        <is>
-          <t>وصول</t>
-        </is>
-      </c>
-      <c r="F155" s="25" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G155" s="25" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="H155" s="26" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="I155" s="27" t="n">
-        <v>0.05556</v>
-      </c>
-      <c r="J155" s="28" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="K155" s="29" t="inlineStr">
-        <is>
-          <t>7م وصول</t>
-        </is>
-      </c>
-      <c r="L155" s="30" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="M155" s="31" t="inlineStr">
-        <is>
-          <t>زيادة وصول العملاء</t>
-        </is>
-      </c>
-      <c r="N155" s="26" t="inlineStr">
-        <is>
-          <t>العملاء</t>
-        </is>
-      </c>
-      <c r="O155" s="32" t="n"/>
-      <c r="P155" s="32" t="n"/>
-      <c r="Q155" s="32" t="n"/>
-      <c r="R155" s="32" t="n"/>
-      <c r="S155" s="32" t="n"/>
-      <c r="T155" s="32" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="U155" s="32" t="n"/>
-      <c r="V155" s="32" t="n"/>
-      <c r="W155" s="32" t="n"/>
-      <c r="X155" s="32" t="n"/>
-      <c r="Y155" s="32" t="n"/>
-      <c r="Z155" s="32" t="n"/>
-      <c r="AA155" s="33">
-        <f>IF($G155="SUM",IF(COUNT($O155:$Z155)=0,"",SUM($O155:$Z155)),IF($G155="AVG",IFERROR(AVERAGE($O155:$Z155),""),IF($G155="LAST",IFERROR(LOOKUP(2,1/($O155:$Z155&lt;&gt;""),$O155:$Z155),""),"")))</f>
-        <v/>
-      </c>
-      <c r="AB155" s="16">
-        <f>IF($J155="","",IF($AA155="","",IF($J155=0,IF($AA155&lt;=0,1,0),IF($F155="↓",IFERROR($J155/$AA155,0),IFERROR($AA155/$J155,0)))))</f>
-        <v/>
-      </c>
-      <c r="AC155" s="15">
-        <f>IF($AB155="","—",IF($AB155&gt;=1,"✅ محقق",IF($AB155&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156" ht="24" customHeight="1">
-      <c r="A156" s="15" t="n">
-        <v>153</v>
-      </c>
-      <c r="B156" s="21" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C156" s="9" t="inlineStr">
-        <is>
-          <t>العلاقات والشراكات</t>
-        </is>
-      </c>
-      <c r="D156" s="9" t="inlineStr">
-        <is>
-          <t>عدد المعارض بالسنة</t>
-        </is>
-      </c>
-      <c r="E156" s="25" t="inlineStr">
-        <is>
-          <t>معرض</t>
-        </is>
-      </c>
-      <c r="F156" s="25" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G156" s="25" t="inlineStr">
-        <is>
-          <t>SUM</t>
-        </is>
-      </c>
-      <c r="H156" s="26" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="I156" s="27" t="n">
-        <v>0.05556</v>
-      </c>
-      <c r="J156" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="K156" s="29" t="inlineStr">
-        <is>
-          <t>3 معارض</t>
-        </is>
-      </c>
-      <c r="L156" s="30" t="inlineStr">
-        <is>
-          <t>الابتكار</t>
-        </is>
-      </c>
-      <c r="M156" s="31" t="inlineStr">
-        <is>
-          <t>إطلاق مشاريع جديدة</t>
-        </is>
-      </c>
-      <c r="N156" s="26" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O156" s="32" t="n"/>
-      <c r="P156" s="32" t="n"/>
-      <c r="Q156" s="32" t="n"/>
-      <c r="R156" s="32" t="n"/>
-      <c r="S156" s="32" t="n"/>
-      <c r="T156" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U156" s="32" t="n"/>
-      <c r="V156" s="32" t="n"/>
-      <c r="W156" s="32" t="n"/>
-      <c r="X156" s="32" t="n"/>
-      <c r="Y156" s="32" t="n"/>
-      <c r="Z156" s="32" t="n"/>
-      <c r="AA156" s="33">
-        <f>IF($G156="SUM",IF(COUNT($O156:$Z156)=0,"",SUM($O156:$Z156)),IF($G156="AVG",IFERROR(AVERAGE($O156:$Z156),""),IF($G156="LAST",IFERROR(LOOKUP(2,1/($O156:$Z156&lt;&gt;""),$O156:$Z156),""),"")))</f>
-        <v/>
-      </c>
-      <c r="AB156" s="16">
-        <f>IF($J156="","",IF($AA156="","",IF($J156=0,IF($AA156&lt;=0,1,0),IF($F156="↓",IFERROR($J156/$AA156,0),IFERROR($AA156/$J156,0)))))</f>
-        <v/>
-      </c>
-      <c r="AC156" s="15">
-        <f>IF($AB156="","—",IF($AB156&gt;=1,"✅ محقق",IF($AB156&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157" ht="24" customHeight="1">
-      <c r="A157" s="15" t="n">
-        <v>154</v>
-      </c>
-      <c r="B157" s="21" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C157" s="9" t="inlineStr">
-        <is>
-          <t>العلاقات والشراكات</t>
-        </is>
-      </c>
-      <c r="D157" s="9" t="inlineStr">
-        <is>
-          <t>اتفاقيات استراتيجية</t>
-        </is>
-      </c>
-      <c r="E157" s="25" t="inlineStr">
-        <is>
-          <t>اتفاقية</t>
-        </is>
-      </c>
-      <c r="F157" s="25" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G157" s="25" t="inlineStr">
-        <is>
-          <t>SUM</t>
-        </is>
-      </c>
-      <c r="H157" s="26" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="I157" s="27" t="n">
-        <v>0.05556</v>
-      </c>
-      <c r="J157" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="K157" s="29" t="inlineStr">
-        <is>
-          <t>3 اتفاقيات</t>
-        </is>
-      </c>
-      <c r="L157" s="30" t="inlineStr">
-        <is>
-          <t>الابتكار</t>
-        </is>
-      </c>
-      <c r="M157" s="31" t="inlineStr">
-        <is>
-          <t>إطلاق مشاريع جديدة</t>
-        </is>
-      </c>
-      <c r="N157" s="26" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O157" s="32" t="n"/>
-      <c r="P157" s="32" t="n"/>
-      <c r="Q157" s="32" t="n"/>
-      <c r="R157" s="32" t="n"/>
-      <c r="S157" s="32" t="n"/>
-      <c r="T157" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U157" s="32" t="n"/>
-      <c r="V157" s="32" t="n"/>
-      <c r="W157" s="32" t="n"/>
-      <c r="X157" s="32" t="n"/>
-      <c r="Y157" s="32" t="n"/>
-      <c r="Z157" s="32" t="n"/>
-      <c r="AA157" s="33">
-        <f>IF($G157="SUM",IF(COUNT($O157:$Z157)=0,"",SUM($O157:$Z157)),IF($G157="AVG",IFERROR(AVERAGE($O157:$Z157),""),IF($G157="LAST",IFERROR(LOOKUP(2,1/($O157:$Z157&lt;&gt;""),$O157:$Z157),""),"")))</f>
-        <v/>
-      </c>
-      <c r="AB157" s="16">
-        <f>IF($J157="","",IF($AA157="","",IF($J157=0,IF($AA157&lt;=0,1,0),IF($F157="↓",IFERROR($J157/$AA157,0),IFERROR($AA157/$J157,0)))))</f>
-        <v/>
-      </c>
-      <c r="AC157" s="15">
-        <f>IF($AB157="","—",IF($AB157&gt;=1,"✅ محقق",IF($AB157&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158" ht="24" customHeight="1">
-      <c r="A158" s="15" t="n">
-        <v>155</v>
-      </c>
-      <c r="B158" s="21" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C158" s="9" t="inlineStr">
-        <is>
-          <t>خدمة العملاء والدعم</t>
-        </is>
-      </c>
-      <c r="D158" s="9" t="inlineStr">
-        <is>
-          <t>تقييم خرائط قوقل</t>
-        </is>
-      </c>
-      <c r="E158" s="25" t="inlineStr">
-        <is>
-          <t>نجمة/5</t>
-        </is>
-      </c>
-      <c r="F158" s="25" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G158" s="25" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="H158" s="26" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="I158" s="27" t="n">
-        <v>0.05556</v>
-      </c>
-      <c r="J158" s="38" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K158" s="29" t="inlineStr">
-        <is>
-          <t>4.7 ⭐</t>
-        </is>
-      </c>
-      <c r="L158" s="30" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="M158" s="31" t="inlineStr">
-        <is>
-          <t>تعزيز تجربة العملاء</t>
-        </is>
-      </c>
-      <c r="N158" s="26" t="inlineStr">
-        <is>
-          <t>العملاء</t>
-        </is>
-      </c>
-      <c r="O158" s="39" t="n"/>
-      <c r="P158" s="39" t="n"/>
-      <c r="Q158" s="39" t="n"/>
-      <c r="R158" s="39" t="n"/>
-      <c r="S158" s="39" t="n"/>
-      <c r="T158" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="U158" s="39" t="n"/>
-      <c r="V158" s="39" t="n"/>
-      <c r="W158" s="39" t="n"/>
-      <c r="X158" s="39" t="n"/>
-      <c r="Y158" s="39" t="n"/>
-      <c r="Z158" s="39" t="n"/>
-      <c r="AA158" s="40">
-        <f>IF($G158="SUM",IF(COUNT($O158:$Z158)=0,"",SUM($O158:$Z158)),IF($G158="AVG",IFERROR(AVERAGE($O158:$Z158),""),IF($G158="LAST",IFERROR(LOOKUP(2,1/($O158:$Z158&lt;&gt;""),$O158:$Z158),""),"")))</f>
-        <v/>
-      </c>
-      <c r="AB158" s="16">
-        <f>IF($J158="","",IF($AA158="","",IF($J158=0,IF($AA158&lt;=0,1,0),IF($F158="↓",IFERROR($J158/$AA158,0),IFERROR($AA158/$J158,0)))))</f>
-        <v/>
-      </c>
-      <c r="AC158" s="15">
-        <f>IF($AB158="","—",IF($AB158&gt;=1,"✅ محقق",IF($AB158&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159" ht="24" customHeight="1">
-      <c r="A159" s="15" t="n">
-        <v>156</v>
-      </c>
-      <c r="B159" s="21" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C159" s="9" t="inlineStr">
-        <is>
-          <t>خدمة العملاء والدعم</t>
-        </is>
-      </c>
-      <c r="D159" s="9" t="inlineStr">
-        <is>
-          <t>معدل خفض الشكاوى</t>
-        </is>
-      </c>
-      <c r="E159" s="25" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F159" s="25" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G159" s="25" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="H159" s="26" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="I159" s="27" t="n">
-        <v>0.05556</v>
-      </c>
-      <c r="J159" s="27" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K159" s="29" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="L159" s="30" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="M159" s="31" t="inlineStr">
-        <is>
-          <t>تعزيز تجربة العملاء</t>
-        </is>
-      </c>
-      <c r="N159" s="26" t="inlineStr">
-        <is>
-          <t>العملاء</t>
-        </is>
-      </c>
-      <c r="O159" s="36" t="n"/>
-      <c r="P159" s="36" t="n"/>
-      <c r="Q159" s="36" t="n"/>
-      <c r="R159" s="36" t="n"/>
-      <c r="S159" s="36" t="n"/>
-      <c r="T159" s="36" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="U159" s="36" t="n"/>
-      <c r="V159" s="36" t="n"/>
-      <c r="W159" s="36" t="n"/>
-      <c r="X159" s="36" t="n"/>
-      <c r="Y159" s="36" t="n"/>
-      <c r="Z159" s="36" t="n"/>
-      <c r="AA159" s="37">
-        <f>IF($G159="SUM",IF(COUNT($O159:$Z159)=0,"",SUM($O159:$Z159)),IF($G159="AVG",IFERROR(AVERAGE($O159:$Z159),""),IF($G159="LAST",IFERROR(LOOKUP(2,1/($O159:$Z159&lt;&gt;""),$O159:$Z159),""),"")))</f>
-        <v/>
-      </c>
-      <c r="AB159" s="16">
-        <f>IF($J159="","",IF($AA159="","",IF($J159=0,IF($AA159&lt;=0,1,0),IF($F159="↓",IFERROR($J159/$AA159,0),IFERROR($AA159/$J159,0)))))</f>
-        <v/>
-      </c>
-      <c r="AC159" s="15">
-        <f>IF($AB159="","—",IF($AB159&gt;=1,"✅ محقق",IF($AB159&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160" ht="24" customHeight="1">
-      <c r="A160" s="15" t="n">
-        <v>157</v>
-      </c>
-      <c r="B160" s="21" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C160" s="9" t="inlineStr">
-        <is>
-          <t>تطبيق تانكي</t>
-        </is>
-      </c>
-      <c r="D160" s="9" t="inlineStr">
-        <is>
-          <t>وصول محتوى تطبيق تانكي</t>
-        </is>
-      </c>
-      <c r="E160" s="25" t="inlineStr">
-        <is>
-          <t>وصول</t>
-        </is>
-      </c>
-      <c r="F160" s="25" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G160" s="25" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="H160" s="26" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="I160" s="27" t="n">
-        <v>0.05556</v>
-      </c>
-      <c r="J160" s="28" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K160" s="29" t="inlineStr">
-        <is>
-          <t>1م وصول</t>
-        </is>
-      </c>
-      <c r="L160" s="30" t="inlineStr">
-        <is>
-          <t>الابتكار</t>
-        </is>
-      </c>
-      <c r="M160" s="31" t="inlineStr">
-        <is>
-          <t>تطبيق «تانكي»</t>
-        </is>
-      </c>
-      <c r="N160" s="26" t="inlineStr">
-        <is>
-          <t>العملاء</t>
-        </is>
-      </c>
-      <c r="O160" s="32" t="n"/>
-      <c r="P160" s="32" t="n"/>
-      <c r="Q160" s="32" t="n"/>
-      <c r="R160" s="32" t="n"/>
-      <c r="S160" s="32" t="n"/>
-      <c r="T160" s="32" t="n"/>
-      <c r="U160" s="32" t="n"/>
-      <c r="V160" s="32" t="n"/>
-      <c r="W160" s="32" t="n"/>
-      <c r="X160" s="32" t="n"/>
-      <c r="Y160" s="32" t="n"/>
-      <c r="Z160" s="32" t="n"/>
-      <c r="AA160" s="33">
-        <f>IF($G160="SUM",IF(COUNT($O160:$Z160)=0,"",SUM($O160:$Z160)),IF($G160="AVG",IFERROR(AVERAGE($O160:$Z160),""),IF($G160="LAST",IFERROR(LOOKUP(2,1/($O160:$Z160&lt;&gt;""),$O160:$Z160),""),"")))</f>
-        <v/>
-      </c>
-      <c r="AB160" s="16">
-        <f>IF($J160="","",IF($AA160="","",IF($J160=0,IF($AA160&lt;=0,1,0),IF($F160="↓",IFERROR($J160/$AA160,0),IFERROR($AA160/$J160,0)))))</f>
-        <v/>
-      </c>
-      <c r="AC160" s="15">
-        <f>IF($AB160="","—",IF($AB160&gt;=1,"✅ محقق",IF($AB160&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161" ht="24" customHeight="1">
-      <c r="A161" s="15" t="n">
-        <v>158</v>
-      </c>
-      <c r="B161" s="21" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C161" s="9" t="inlineStr">
-        <is>
-          <t>تطبيق تانكي</t>
-        </is>
-      </c>
-      <c r="D161" s="9" t="inlineStr">
-        <is>
-          <t>مشاركات تطبيق تانكي</t>
-        </is>
-      </c>
-      <c r="E161" s="25" t="inlineStr">
-        <is>
-          <t>مشاركة</t>
-        </is>
-      </c>
-      <c r="F161" s="25" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G161" s="25" t="inlineStr">
-        <is>
-          <t>SUM</t>
-        </is>
-      </c>
-      <c r="H161" s="26" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="I161" s="27" t="n">
-        <v>0.05556</v>
-      </c>
-      <c r="J161" s="28" t="n">
-        <v>250</v>
-      </c>
-      <c r="K161" s="29" t="inlineStr">
-        <is>
-          <t>250 مشاركة</t>
-        </is>
-      </c>
-      <c r="L161" s="30" t="inlineStr">
-        <is>
-          <t>الابتكار</t>
-        </is>
-      </c>
-      <c r="M161" s="31" t="inlineStr">
-        <is>
-          <t>تطبيق «تانكي»</t>
-        </is>
-      </c>
-      <c r="N161" s="26" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="O161" s="32" t="n"/>
-      <c r="P161" s="32" t="n"/>
-      <c r="Q161" s="32" t="n"/>
-      <c r="R161" s="32" t="n"/>
-      <c r="S161" s="32" t="n"/>
-      <c r="T161" s="32" t="n"/>
-      <c r="U161" s="32" t="n"/>
-      <c r="V161" s="32" t="n"/>
-      <c r="W161" s="32" t="n"/>
-      <c r="X161" s="32" t="n"/>
-      <c r="Y161" s="32" t="n"/>
-      <c r="Z161" s="32" t="n"/>
-      <c r="AA161" s="33">
-        <f>IF($G161="SUM",IF(COUNT($O161:$Z161)=0,"",SUM($O161:$Z161)),IF($G161="AVG",IFERROR(AVERAGE($O161:$Z161),""),IF($G161="LAST",IFERROR(LOOKUP(2,1/($O161:$Z161&lt;&gt;""),$O161:$Z161),""),"")))</f>
-        <v/>
-      </c>
-      <c r="AB161" s="16">
-        <f>IF($J161="","",IF($AA161="","",IF($J161=0,IF($AA161&lt;=0,1,0),IF($F161="↓",IFERROR($J161/$AA161,0),IFERROR($AA161/$J161,0)))))</f>
-        <v/>
-      </c>
-      <c r="AC161" s="15">
-        <f>IF($AB161="","—",IF($AB161&gt;=1,"✅ محقق",IF($AB161&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:AC161"/>
+  <autoFilter ref="A3:AC146"/>
   <mergeCells count="2">
     <mergeCell ref="A2:AC2"/>
     <mergeCell ref="A1:AC1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66 O67 O68 O69 O70 O71 O72 O73 O74 O75 O76 O77 O78 O79 O80 O81 O82 O83 O84 O85 O86 O87 O88 O89 O90 O91 O92 O93 O94 O95 O96 O97 O98 O99 O100 O101 O102 O103 O104 O105 O106 O107 O108 O109 O110 O111 O112 O113 O114 O115 O116 O117 O118 O119 O120 O121 O122 O123 O124 O125 O126 O127 O128 O129 O130 O131 O132 O133 O134 O135 O136 O137 O138 O139 O140 O141 O142 O143 O144 O145 O146 O147 O148 O149 O150 O151 O152 O153 O154 O155 O156 O157 O158 O159 O160 O161 P4 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 P34 P35 P36 P37 P38 P39 P40 P41 P42 P43 P44 P45 P46 P47 P48 P49 P50 P51 P52 P53 P54 P55 P56 P57 P58 P59 P60 P61 P62 P63 P64 P65 P66 P67 P68 P69 P70 P71 P72 P73 P74 P75 P76 P77 P78 P79 P80 P81 P82 P83 P84 P85 P86 P87 P88 P89 P90 P91 P92 P93 P94 P95 P96 P97 P98 P99 P100 P101 P102 P103 P104 P105 P106 P107 P108 P109 P110 P111 P112 P113 P114 P115 P116 P117 P118 P119 P120 P121 P122 P123 P124 P125 P126 P127 P128 P129 P130 P131 P132 P133 P134 P135 P136 P137 P138 P139 P140 P141 P142 P143 P144 P145 P146 P147 P148 P149 P150 P151 P152 P153 P154 P155 P156 P157 P158 P159 P160 P161 Q4 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 Q34 Q35 Q36 Q37 Q38 Q39 Q40 Q41 Q42 Q43 Q44 Q45 Q46 Q47 Q48 Q49 Q50 Q51 Q52 Q53 Q54 Q55 Q56 Q57 Q58 Q59 Q60 Q61 Q62 Q63 Q64 Q65 Q66 Q67 Q68 Q69 Q70 Q71 Q72 Q73 Q74 Q75 Q76 Q77 Q78 Q79 Q80 Q81 Q82 Q83 Q84 Q85 Q86 Q87 Q88 Q89 Q90 Q91 Q92 Q93 Q94 Q95 Q96 Q97 Q98 Q99 Q100 Q101 Q102 Q103 Q104 Q105 Q106 Q107 Q108 Q109 Q110 Q111 Q112 Q113 Q114 Q115 Q116 Q117 Q118 Q119 Q120 Q121 Q122 Q123 Q124 Q125 Q126 Q127 Q128 Q129 Q130 Q131 Q132 Q133 Q134 Q135 Q136 Q137 Q138 Q139 Q140 Q141 Q142 Q143 Q144 Q145 Q146 Q147 Q148 Q149 Q150 Q151 Q152 Q153 Q154 Q155 Q156 Q157 Q158 Q159 Q160 Q161 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93 R94 R95 R96 R97 R98 R99 R100 R101 R102 R103 R104 R105 R106 R107 R108 R109 R110 R111 R112 R113 R114 R115 R116 R117 R118 R119 R120 R121 R122 R123 R124 R125 R126 R127 R128 R129 R130 R131 R132 R133 R134 R135 R136 R137 R138 R139 R140 R141 R142 R143 R144 R145 R146 R147 R148 R149 R150 R151 R152 R153 R154 R155 R156 R157 R158 R159 R160 R161 S4 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 S31 S32 S33 S34 S35 S36 S37 S38 S39 S40 S41 S42 S43 S44 S45 S46 S47 S48 S49 S50 S51 S52 S53 S54 S55 S56 S57 S58 S59 S60 S61 S62 S63 S64 S65 S66 S67 S68 S69 S70 S71 S72 S73 S74 S75 S76 S77 S78 S79 S80 S81 S82 S83 S84 S85 S86 S87 S88 S89 S90 S91 S92 S93 S94 S95 S96 S97 S98 S99 S100 S101 S102 S103 S104 S105 S106 S107 S108 S109 S110 S111 S112 S113 S114 S115 S116 S117 S118 S119 S120 S121 S122 S123 S124 S125 S126 S127 S128 S129 S130 S131 S132 S133 S134 S135 S136 S137 S138 S139 S140 S141 S142 S143 S144 S145 S146 S147 S148 S149 S150 S151 S152 S153 S154 S155 S156 S157 S158 S159 S160 S161 T4 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 T34 T35 T36 T37 T38 T39 T40 T41 T42 T43 T44 T45 T46 T47 T48 T49 T50 T51 T52 T53 T54 T55 T56 T57 T58 T59 T60 T61 T62 T63 T64 T65 T66 T67 T68 T69 T70 T71 T72 T73 T74 T75 T76 T77 T78 T79 T80 T81 T82 T83 T84 T85 T86 T87 T88 T89 T90 T91 T92 T93 T94 T95 T96 T97 T98 T99 T100 T101 T102 T103 T104 T105 T106 T107 T108 T109 T110 T111 T112 T113 T114 T115 T116 T117 T118 T119 T120 T121 T122 T123 T124 T125 T126 T127 T128 T129 T130 T131 T132 T133 T134 T135 T136 T137 T138 T139 T140 T141 T142 T143 T144 T145 T146 T147 T148 T149 T150 T151 T152 T153 T154 T155 T156 T157 T158 T159 T160 T161 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 V4 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 V31 V32 V33 V34 V35 V36 V37 V38 V39 V40 V41 V42 V43 V44 V45 V46 V47 V48 V49 V50 V51 V52 V53 V54 V55 V56 V57 V58 V59 V60 V61 V62 V63 V64 V65 V66 V67 V68 V69 V70 V71 V72 V73 V74 V75 V76 V77 V78 V79 V80 V81 V82 V83 V84 V85 V86 V87 V88 V89 V90 V91 V92 V93 V94 V95 V96 V97 V98 V99 V100 V101 V102 V103 V104 V105 V106 V107 V108 V109 V110 V111 V112 V113 V114 V115 V116 V117 V118 V119 V120 V121 V122 V123 V124 V125 V126 V127 V128 V129 V130 V131 V132 V133 V134 V135 V136 V137 V138 V139 V140 V141 V142 V143 V144 V145 V146 V147 V148 V149 V150 V151 V152 V153 V154 V155 V156 V157 V158 V159 V160 V161 W4 W5 W6 W7 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 W31 W32 W33 W34 W35 W36 W37 W38 W39 W40 W41 W42 W43 W44 W45 W46 W47 W48 W49 W50 W51 W52 W53 W54 W55 W56 W57 W58 W59 W60 W61 W62 W63 W64 W65 W66 W67 W68 W69 W70 W71 W72 W73 W74 W75 W76 W77 W78 W79 W80 W81 W82 W83 W84 W85 W86 W87 W88 W89 W90 W91 W92 W93 W94 W95 W96 W97 W98 W99 W100 W101 W102 W103 W104 W105 W106 W107 W108 W109 W110 W111 W112 W113 W114 W115 W116 W117 W118 W119 W120 W121 W122 W123 W124 W125 W126 W127 W128 W129 W130 W131 W132 W133 W134 W135 W136 W137 W138 W139 W140 W141 W142 W143 W144 W145 W146 W147 W148 W149 W150 W151 W152 W153 W154 W155 W156 W157 W158 W159 W160 W161 X4 X5 X6 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30 X31 X32 X33 X34 X35 X36 X37 X38 X39 X40 X41 X42 X43 X44 X45 X46 X47 X48 X49 X50 X51 X52 X53 X54 X55 X56 X57 X58 X59 X60 X61 X62 X63 X64 X65 X66 X67 X68 X69 X70 X71 X72 X73 X74 X75 X76 X77 X78 X79 X80 X81 X82 X83 X84 X85 X86 X87 X88 X89 X90 X91 X92 X93 X94 X95 X96 X97 X98 X99 X100 X101 X102 X103 X104 X105 X106 X107 X108 X109 X110 X111 X112 X113 X114 X115 X116 X117 X118 X119 X120 X121 X122 X123 X124 X125 X126 X127 X128 X129 X130 X131 X132 X133 X134 X135 X136 X137 X138 X139 X140 X141 X142 X143 X144 X145 X146 X147 X148 X149 X150 X151 X152 X153 X154 X155 X156 X157 X158 X159 X160 X161 Y4 Y5 Y6 Y7 Y8 Y9 Y10 Y11 Y12 Y13 Y14 Y15 Y16 Y17 Y18 Y19 Y20 Y21 Y22 Y23 Y24 Y25 Y26 Y27 Y28 Y29 Y30 Y31 Y32 Y33 Y34 Y35 Y36 Y37 Y38 Y39 Y40 Y41 Y42 Y43 Y44 Y45 Y46 Y47 Y48 Y49 Y50 Y51 Y52 Y53 Y54 Y55 Y56 Y57 Y58 Y59 Y60 Y61 Y62 Y63 Y64 Y65 Y66 Y67 Y68 Y69 Y70 Y71 Y72 Y73 Y74 Y75 Y76 Y77 Y78 Y79 Y80 Y81 Y82 Y83 Y84 Y85 Y86 Y87 Y88 Y89 Y90 Y91 Y92 Y93 Y94 Y95 Y96 Y97 Y98 Y99 Y100 Y101 Y102 Y103 Y104 Y105 Y106 Y107 Y108 Y109 Y110 Y111 Y112 Y113 Y114 Y115 Y116 Y117 Y118 Y119 Y120 Y121 Y122 Y123 Y124 Y125 Y126 Y127 Y128 Y129 Y130 Y131 Y132 Y133 Y134 Y135 Y136 Y137 Y138 Y139 Y140 Y141 Y142 Y143 Y144 Y145 Y146 Y147 Y148 Y149 Y150 Y151 Y152 Y153 Y154 Y155 Y156 Y157 Y158 Y159 Y160 Y161 Z4 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12 Z13 Z14 Z15 Z16 Z17 Z18 Z19 Z20 Z21 Z22 Z23 Z24 Z25 Z26 Z27 Z28 Z29 Z30 Z31 Z32 Z33 Z34 Z35 Z36 Z37 Z38 Z39 Z40 Z41 Z42 Z43 Z44 Z45 Z46 Z47 Z48 Z49 Z50 Z51 Z52 Z53 Z54 Z55 Z56 Z57 Z58 Z59 Z60 Z61 Z62 Z63 Z64 Z65 Z66 Z67 Z68 Z69 Z70 Z71 Z72 Z73 Z74 Z75 Z76 Z77 Z78 Z79 Z80 Z81 Z82 Z83 Z84 Z85 Z86 Z87 Z88 Z89 Z90 Z91 Z92 Z93 Z94 Z95 Z96 Z97 Z98 Z99 Z100 Z101 Z102 Z103 Z104 Z105 Z106 Z107 Z108 Z109 Z110 Z111 Z112 Z113 Z114 Z115 Z116 Z117 Z118 Z119 Z120 Z121 Z122 Z123 Z124 Z125 Z126 Z127 Z128 Z129 Z130 Z131 Z132 Z133 Z134 Z135 Z136 Z137 Z138 Z139 Z140 Z141 Z142 Z143 Z144 Z145 Z146 Z147 Z148 Z149 Z150 Z151 Z152 Z153 Z154 Z155 Z156 Z157 Z158 Z159 Z160 Z161" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66 O67 O68 O69 O70 O71 O72 O73 O74 O75 O76 O77 O78 O79 O80 O81 O82 O83 O84 O85 O86 O87 O88 O89 O90 O91 O92 O93 O94 O95 O96 O97 O98 O99 O100 O101 O102 O103 O104 O105 O106 O107 O108 O109 O110 O111 O112 O113 O114 O115 O116 O117 O118 O119 O120 O121 O122 O123 O124 O125 O126 O127 O128 O129 O130 O131 O132 O133 O134 O135 O136 O137 O138 O139 O140 O141 O142 O143 O144 O145 O146 P4 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 P34 P35 P36 P37 P38 P39 P40 P41 P42 P43 P44 P45 P46 P47 P48 P49 P50 P51 P52 P53 P54 P55 P56 P57 P58 P59 P60 P61 P62 P63 P64 P65 P66 P67 P68 P69 P70 P71 P72 P73 P74 P75 P76 P77 P78 P79 P80 P81 P82 P83 P84 P85 P86 P87 P88 P89 P90 P91 P92 P93 P94 P95 P96 P97 P98 P99 P100 P101 P102 P103 P104 P105 P106 P107 P108 P109 P110 P111 P112 P113 P114 P115 P116 P117 P118 P119 P120 P121 P122 P123 P124 P125 P126 P127 P128 P129 P130 P131 P132 P133 P134 P135 P136 P137 P138 P139 P140 P141 P142 P143 P144 P145 P146 Q4 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 Q34 Q35 Q36 Q37 Q38 Q39 Q40 Q41 Q42 Q43 Q44 Q45 Q46 Q47 Q48 Q49 Q50 Q51 Q52 Q53 Q54 Q55 Q56 Q57 Q58 Q59 Q60 Q61 Q62 Q63 Q64 Q65 Q66 Q67 Q68 Q69 Q70 Q71 Q72 Q73 Q74 Q75 Q76 Q77 Q78 Q79 Q80 Q81 Q82 Q83 Q84 Q85 Q86 Q87 Q88 Q89 Q90 Q91 Q92 Q93 Q94 Q95 Q96 Q97 Q98 Q99 Q100 Q101 Q102 Q103 Q104 Q105 Q106 Q107 Q108 Q109 Q110 Q111 Q112 Q113 Q114 Q115 Q116 Q117 Q118 Q119 Q120 Q121 Q122 Q123 Q124 Q125 Q126 Q127 Q128 Q129 Q130 Q131 Q132 Q133 Q134 Q135 Q136 Q137 Q138 Q139 Q140 Q141 Q142 Q143 Q144 Q145 Q146 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93 R94 R95 R96 R97 R98 R99 R100 R101 R102 R103 R104 R105 R106 R107 R108 R109 R110 R111 R112 R113 R114 R115 R116 R117 R118 R119 R120 R121 R122 R123 R124 R125 R126 R127 R128 R129 R130 R131 R132 R133 R134 R135 R136 R137 R138 R139 R140 R141 R142 R143 R144 R145 R146 S4 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 S31 S32 S33 S34 S35 S36 S37 S38 S39 S40 S41 S42 S43 S44 S45 S46 S47 S48 S49 S50 S51 S52 S53 S54 S55 S56 S57 S58 S59 S60 S61 S62 S63 S64 S65 S66 S67 S68 S69 S70 S71 S72 S73 S74 S75 S76 S77 S78 S79 S80 S81 S82 S83 S84 S85 S86 S87 S88 S89 S90 S91 S92 S93 S94 S95 S96 S97 S98 S99 S100 S101 S102 S103 S104 S105 S106 S107 S108 S109 S110 S111 S112 S113 S114 S115 S116 S117 S118 S119 S120 S121 S122 S123 S124 S125 S126 S127 S128 S129 S130 S131 S132 S133 S134 S135 S136 S137 S138 S139 S140 S141 S142 S143 S144 S145 S146 T4 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 T34 T35 T36 T37 T38 T39 T40 T41 T42 T43 T44 T45 T46 T47 T48 T49 T50 T51 T52 T53 T54 T55 T56 T57 T58 T59 T60 T61 T62 T63 T64 T65 T66 T67 T68 T69 T70 T71 T72 T73 T74 T75 T76 T77 T78 T79 T80 T81 T82 T83 T84 T85 T86 T87 T88 T89 T90 T91 T92 T93 T94 T95 T96 T97 T98 T99 T100 T101 T102 T103 T104 T105 T106 T107 T108 T109 T110 T111 T112 T113 T114 T115 T116 T117 T118 T119 T120 T121 T122 T123 T124 T125 T126 T127 T128 T129 T130 T131 T132 T133 T134 T135 T136 T137 T138 T139 T140 T141 T142 T143 T144 T145 T146 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 V4 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 V31 V32 V33 V34 V35 V36 V37 V38 V39 V40 V41 V42 V43 V44 V45 V46 V47 V48 V49 V50 V51 V52 V53 V54 V55 V56 V57 V58 V59 V60 V61 V62 V63 V64 V65 V66 V67 V68 V69 V70 V71 V72 V73 V74 V75 V76 V77 V78 V79 V80 V81 V82 V83 V84 V85 V86 V87 V88 V89 V90 V91 V92 V93 V94 V95 V96 V97 V98 V99 V100 V101 V102 V103 V104 V105 V106 V107 V108 V109 V110 V111 V112 V113 V114 V115 V116 V117 V118 V119 V120 V121 V122 V123 V124 V125 V126 V127 V128 V129 V130 V131 V132 V133 V134 V135 V136 V137 V138 V139 V140 V141 V142 V143 V144 V145 V146 W4 W5 W6 W7 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 W31 W32 W33 W34 W35 W36 W37 W38 W39 W40 W41 W42 W43 W44 W45 W46 W47 W48 W49 W50 W51 W52 W53 W54 W55 W56 W57 W58 W59 W60 W61 W62 W63 W64 W65 W66 W67 W68 W69 W70 W71 W72 W73 W74 W75 W76 W77 W78 W79 W80 W81 W82 W83 W84 W85 W86 W87 W88 W89 W90 W91 W92 W93 W94 W95 W96 W97 W98 W99 W100 W101 W102 W103 W104 W105 W106 W107 W108 W109 W110 W111 W112 W113 W114 W115 W116 W117 W118 W119 W120 W121 W122 W123 W124 W125 W126 W127 W128 W129 W130 W131 W132 W133 W134 W135 W136 W137 W138 W139 W140 W141 W142 W143 W144 W145 W146 X4 X5 X6 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30 X31 X32 X33 X34 X35 X36 X37 X38 X39 X40 X41 X42 X43 X44 X45 X46 X47 X48 X49 X50 X51 X52 X53 X54 X55 X56 X57 X58 X59 X60 X61 X62 X63 X64 X65 X66 X67 X68 X69 X70 X71 X72 X73 X74 X75 X76 X77 X78 X79 X80 X81 X82 X83 X84 X85 X86 X87 X88 X89 X90 X91 X92 X93 X94 X95 X96 X97 X98 X99 X100 X101 X102 X103 X104 X105 X106 X107 X108 X109 X110 X111 X112 X113 X114 X115 X116 X117 X118 X119 X120 X121 X122 X123 X124 X125 X126 X127 X128 X129 X130 X131 X132 X133 X134 X135 X136 X137 X138 X139 X140 X141 X142 X143 X144 X145 X146 Y4 Y5 Y6 Y7 Y8 Y9 Y10 Y11 Y12 Y13 Y14 Y15 Y16 Y17 Y18 Y19 Y20 Y21 Y22 Y23 Y24 Y25 Y26 Y27 Y28 Y29 Y30 Y31 Y32 Y33 Y34 Y35 Y36 Y37 Y38 Y39 Y40 Y41 Y42 Y43 Y44 Y45 Y46 Y47 Y48 Y49 Y50 Y51 Y52 Y53 Y54 Y55 Y56 Y57 Y58 Y59 Y60 Y61 Y62 Y63 Y64 Y65 Y66 Y67 Y68 Y69 Y70 Y71 Y72 Y73 Y74 Y75 Y76 Y77 Y78 Y79 Y80 Y81 Y82 Y83 Y84 Y85 Y86 Y87 Y88 Y89 Y90 Y91 Y92 Y93 Y94 Y95 Y96 Y97 Y98 Y99 Y100 Y101 Y102 Y103 Y104 Y105 Y106 Y107 Y108 Y109 Y110 Y111 Y112 Y113 Y114 Y115 Y116 Y117 Y118 Y119 Y120 Y121 Y122 Y123 Y124 Y125 Y126 Y127 Y128 Y129 Y130 Y131 Y132 Y133 Y134 Y135 Y136 Y137 Y138 Y139 Y140 Y141 Y142 Y143 Y144 Y145 Y146 Z4 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12 Z13 Z14 Z15 Z16 Z17 Z18 Z19 Z20 Z21 Z22 Z23 Z24 Z25 Z26 Z27 Z28 Z29 Z30 Z31 Z32 Z33 Z34 Z35 Z36 Z37 Z38 Z39 Z40 Z41 Z42 Z43 Z44 Z45 Z46 Z47 Z48 Z49 Z50 Z51 Z52 Z53 Z54 Z55 Z56 Z57 Z58 Z59 Z60 Z61 Z62 Z63 Z64 Z65 Z66 Z67 Z68 Z69 Z70 Z71 Z72 Z73 Z74 Z75 Z76 Z77 Z78 Z79 Z80 Z81 Z82 Z83 Z84 Z85 Z86 Z87 Z88 Z89 Z90 Z91 Z92 Z93 Z94 Z95 Z96 Z97 Z98 Z99 Z100 Z101 Z102 Z103 Z104 Z105 Z106 Z107 Z108 Z109 Z110 Z111 Z112 Z113 Z114 Z115 Z116 Z117 Z118 Z119 Z120 Z121 Z122 Z123 Z124 Z125 Z126 Z127 Z128 Z129 Z130 Z131 Z132 Z133 Z134 Z135 Z136 Z137 Z138 Z139 Z140 Z141 Z142 Z143 Z144 Z145 Z146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/درب-سجل-المؤشرات-الموحّد-2026.xlsx
+++ b/درب-سجل-المؤشرات-الموحّد-2026.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الاستراتيجية" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="اللوحة الموجزة" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="سجل المؤشرات" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="سجل المشاريع" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'سجل المؤشرات'!$A$3:$AC$146</definedName>
@@ -248,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -368,6 +369,25 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -14634,4 +14654,453 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>سجل المبادرات والمشاريع — مشاريع إدارة التقنية (تغذّي مؤشر «إنجاز المحفظة»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>المشروع</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>الكمية</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>نوع الكمية</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>المنجز</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>نسبة الإنجاز</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>الإدارة</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>المؤشر المرتبط</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>نظام أتمتة الكاش (Cash-In)</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>164</v>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E3" s="41" t="n">
+        <v>59</v>
+      </c>
+      <c r="F3" s="16">
+        <f>IFERROR(E3/C3,0)</f>
+        <v/>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
+      <c r="H3" s="42" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>D365 FNO — المرحلة الأولى</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>وحدة</t>
+        </is>
+      </c>
+      <c r="E4" s="41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F4" s="16">
+        <f>IFERROR(E4/C4,0)</f>
+        <v/>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
+      <c r="H4" s="42" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>D365 FNO — المرحلة الثانية</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>وحدة</t>
+        </is>
+      </c>
+      <c r="E5" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="16">
+        <f>IFERROR(E5/C5,0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
+      <c r="H5" s="42" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>D365 FNO — المرحلة الثالثة</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>وحدة</t>
+        </is>
+      </c>
+      <c r="E6" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="16">
+        <f>IFERROR(E6/C6,0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
+      <c r="H6" s="42" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>تطبيق الامتياز مع واثق</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>تطبيق</t>
+        </is>
+      </c>
+      <c r="E7" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="16">
+        <f>IFERROR(E7/C7,0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
+      <c r="H7" s="42" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>ربط المحطات بوزارة الطاقة (ATJ)</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>164</v>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E8" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="16">
+        <f>IFERROR(E8/C8,0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
+      <c r="H8" s="42" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>ربط الكاميرات بالمركز الرئيسي</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>164</v>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E9" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="16">
+        <f>IFERROR(E9/C9,0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
+      <c r="H9" s="42" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>تطبيق الولاء (تانكي) في المحطات</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>164</v>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E10" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="16">
+        <f>IFERROR(E10/C10,0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
+      <c r="H10" s="42" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>منصة Tatin السحابية</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>164</v>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E11" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="16">
+        <f>IFERROR(E11/C11,0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
+      <c r="H11" s="42" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>إدارة العمليات بالذكاء الاصطناعي</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>164</v>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E12" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="16">
+        <f>IFERROR(E12/C12,0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
+      <c r="H12" s="42" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr"/>
+      <c r="B13" s="44" t="inlineStr">
+        <is>
+          <t>إجمالي إنجاز المحفظة (مرجّح بالكمية)</t>
+        </is>
+      </c>
+      <c r="C13" s="45">
+        <f>SUM(C3:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="43" t="inlineStr"/>
+      <c r="E13" s="45">
+        <f>SUM(E3:E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="46">
+        <f>IFERROR(E13/C13,0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="43" t="inlineStr"/>
+      <c r="H13" s="43" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>